--- a/important_mails_2026-04-16.xlsx
+++ b/important_mails_2026-04-16.xlsx
@@ -1491,7 +1491,7 @@
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>法务/侵权类</t>
+          <t>货件/库存类</t>
         </is>
       </c>
       <c r="B22" s="2" t="inlineStr">
@@ -1506,65 +1506,21 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>Thu, 9 Apr 2026 08:46:52 +0000</t>
+          <t>Tue, 14 Apr 2026 18:58:06 +0000</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
+          <t>Fulfilment by Amazon &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>Addebito delle tariffe di rimozione e per reimpiego quando le unità vengono elaborate</t>
+          <t>Create FBA removal order by 2026-04-23</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr"/>
       <c r="H22" s="2" t="inlineStr">
-        <is>
-          <t>96
- Le tariffe per gli ordini di rimozione e di reimpiego di inventario di Logistica di Amazon verranno ora addebitate per unità ogni volta che un'unità viene rimossa o destinata ad altro uso.
- Buongiorno,
- a partire dal 1° maggio 2026, le tariffe per gli ordini di rimozione e di reimpiego di inventario di Logistica di Amazon verranno addebitate per unità nel momento in cui ciascuna unità viene rimossa o destinata ad altro uso. Questo aggiornamento è in linea con gli standard del settore e offre una maggiore visibilità sulle attività di rimozione e reimpiego di inventario.
- Questa modifica riguarda solo i casi in cui ti viene addebitato il costo. Le tariffe per gli ordini di rimozione e di reimpiego di inventario rimangono invariate. In precedenza, queste tariffe venivano addebitate una volta completato l'intero ordine di rimozione o di reimpiego di inventario.
- A questo proposito, non è richiesto alcun intervento da parte tua. Questa modifica verrà applicata automaticamente ai nuovi ordini di rimozione e di reimpiego di inventario creati a partire dal 1° maggio.
- Per consultare i costi di rimozione e reimpiego di inventario a livello di spedizione e verificare quando le unità veng</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" s="2" t="inlineStr">
-        <is>
-          <t>货件/库存类</t>
-        </is>
-      </c>
-      <c r="B23" s="2" t="inlineStr">
-        <is>
-          <t>last7</t>
-        </is>
-      </c>
-      <c r="C23" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D23" s="2" t="inlineStr">
-        <is>
-          <t>Tue, 14 Apr 2026 18:58:06 +0000</t>
-        </is>
-      </c>
-      <c r="E23" s="2" t="inlineStr">
-        <is>
-          <t>Fulfilment by Amazon &lt;donotreply@amazon.com&gt;</t>
-        </is>
-      </c>
-      <c r="F23" s="2" t="inlineStr">
-        <is>
-          <t>Create FBA removal order by 2026-04-23</t>
-        </is>
-      </c>
-      <c r="G23" s="2" t="inlineStr"/>
-      <c r="H23" s="2" t="inlineStr">
         <is>
           <t>96
 Automated removals of unfulfillable inventory
@@ -1585,39 +1541,39 @@
         </is>
       </c>
     </row>
-    <row r="24">
-      <c r="A24" s="2" t="inlineStr">
+    <row r="23">
+      <c r="A23" s="2" t="inlineStr">
         <is>
           <t>货件/库存类</t>
         </is>
       </c>
-      <c r="B24" s="2" t="inlineStr">
+      <c r="B23" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C24" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D24" s="2" t="inlineStr">
+      <c r="C23" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
         <is>
           <t>Tue, 14 Apr 2026 18:27:29 +0000</t>
         </is>
       </c>
-      <c r="E24" s="2" t="inlineStr">
+      <c r="E23" s="2" t="inlineStr">
         <is>
           <t>Fulfilment by Amazon &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F24" s="2" t="inlineStr">
+      <c r="F23" s="2" t="inlineStr">
         <is>
           <t>Disposal order created for unsellable FBA inventory</t>
         </is>
       </c>
-      <c r="G24" s="2" t="inlineStr"/>
-      <c r="H24" s="2" t="inlineStr">
+      <c r="G23" s="2" t="inlineStr"/>
+      <c r="H23" s="2" t="inlineStr">
         <is>
           <t>96
 Automated Removals of Unfulfillable Inventory
@@ -1640,39 +1596,39 @@
         </is>
       </c>
     </row>
-    <row r="25">
-      <c r="A25" s="2" t="inlineStr">
+    <row r="24">
+      <c r="A24" s="2" t="inlineStr">
         <is>
           <t>其他风险类</t>
         </is>
       </c>
-      <c r="B25" s="2" t="inlineStr">
+      <c r="B24" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C25" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D25" s="2" t="inlineStr">
+      <c r="C24" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
         <is>
           <t>Fri, 10 Apr 2026 14:20:37 +0000</t>
         </is>
       </c>
-      <c r="E25" s="2" t="inlineStr">
+      <c r="E24" s="2" t="inlineStr">
         <is>
           <t>Amazon Europe &lt;noreply@sell.amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F25" s="2" t="inlineStr">
+      <c r="F24" s="2" t="inlineStr">
         <is>
           <t>Get discounts up to €500 per shipment by expanding to Europe!</t>
         </is>
       </c>
-      <c r="G25" s="2" t="inlineStr"/>
-      <c r="H25" s="2" t="inlineStr">
+      <c r="G24" s="2" t="inlineStr"/>
+      <c r="H24" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">[Amazon logo](https://go.amazonsellerservices.com/e/229492/-logo/7z2qvdy/6598918207/h/oQJ3hcZAc232rnIjbHrMLH2dvtBVfEq_dAzSA60S8Es)
 C2S2 PCP Pallet Limited Time Promotion
@@ -1688,39 +1644,39 @@
         </is>
       </c>
     </row>
-    <row r="26">
-      <c r="A26" s="2" t="inlineStr">
+    <row r="25">
+      <c r="A25" s="2" t="inlineStr">
         <is>
           <t>其他风险类</t>
         </is>
       </c>
-      <c r="B26" s="2" t="inlineStr">
+      <c r="B25" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C26" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D26" s="2" t="inlineStr">
+      <c r="C25" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D25" s="2" t="inlineStr">
         <is>
           <t>Thu, 9 Apr 2026 11:27:28 +0000</t>
         </is>
       </c>
-      <c r="E26" s="2" t="inlineStr">
+      <c r="E25" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F26" s="2" t="inlineStr">
+      <c r="F25" s="2" t="inlineStr">
         <is>
           <t>FBA removal and disposal fees to be charged as units are processed</t>
         </is>
       </c>
-      <c r="G26" s="2" t="inlineStr"/>
-      <c r="H26" s="2" t="inlineStr">
+      <c r="G25" s="2" t="inlineStr"/>
+      <c r="H25" s="2" t="inlineStr">
         <is>
           <t>96
  FBA removal and disposal fees will now be charged on a per-unit basis at the time each unit is removed or disposed of.
@@ -1740,39 +1696,39 @@
         </is>
       </c>
     </row>
-    <row r="27">
-      <c r="A27" s="2" t="inlineStr">
+    <row r="26">
+      <c r="A26" s="2" t="inlineStr">
         <is>
           <t>其他风险类</t>
         </is>
       </c>
-      <c r="B27" s="2" t="inlineStr">
+      <c r="B26" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C27" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D27" s="2" t="inlineStr">
+      <c r="C26" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D26" s="2" t="inlineStr">
         <is>
           <t>Thu, 9 Apr 2026 10:52:42 +0000</t>
         </is>
       </c>
-      <c r="E27" s="2" t="inlineStr">
+      <c r="E26" s="2" t="inlineStr">
         <is>
           <t>Amazon Services Europe &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F27" s="2" t="inlineStr">
+      <c r="F26" s="2" t="inlineStr">
         <is>
           <t>FBA removal and disposal fees to be charged as units are processed</t>
         </is>
       </c>
-      <c r="G27" s="2" t="inlineStr"/>
-      <c r="H27" s="2" t="inlineStr">
+      <c r="G26" s="2" t="inlineStr"/>
+      <c r="H26" s="2" t="inlineStr">
         <is>
           <t>96
  FBA removal and disposal fees will now be charged on a per-unit basis at the time that each unit is removed or disposed of.
@@ -1791,39 +1747,39 @@
         </is>
       </c>
     </row>
-    <row r="28">
-      <c r="A28" s="2" t="inlineStr">
+    <row r="27">
+      <c r="A27" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B28" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C28" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D28" s="2" t="inlineStr">
+      <c r="B27" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C27" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D27" s="2" t="inlineStr">
         <is>
           <t>Wed, 8 Apr 2026 02:11:54 +0000</t>
         </is>
       </c>
-      <c r="E28" s="2" t="inlineStr">
+      <c r="E27" s="2" t="inlineStr">
         <is>
           <t>"Amazon.com" &lt;fba-noreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F28" s="2" t="inlineStr">
+      <c r="F27" s="2" t="inlineStr">
         <is>
           <t>Your FBA removal request is complete (W4mGNrNTVu)</t>
         </is>
       </c>
-      <c r="G28" s="2" t="inlineStr"/>
-      <c r="H28" s="2" t="inlineStr">
+      <c r="G27" s="2" t="inlineStr"/>
+      <c r="H27" s="2" t="inlineStr">
         <is>
           <t>Greetings from Amazon.com
 We thought you'd like to know that we have completed and shipped your removal
@@ -1849,39 +1805,39 @@
         </is>
       </c>
     </row>
-    <row r="29">
-      <c r="A29" s="2" t="inlineStr">
+    <row r="28">
+      <c r="A28" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B29" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C29" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D29" s="2" t="inlineStr">
+      <c r="B28" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C28" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D28" s="2" t="inlineStr">
         <is>
           <t>Mon, 6 Apr 2026 15:50:12 +0000</t>
         </is>
       </c>
-      <c r="E29" s="2" t="inlineStr">
+      <c r="E28" s="2" t="inlineStr">
         <is>
           <t>Fulfillment by Amazon Operations &lt;fba-noreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F29" s="2" t="inlineStr">
+      <c r="F28" s="2" t="inlineStr">
         <is>
           <t>Automated unfulfillable FBA inventory removal notification</t>
         </is>
       </c>
-      <c r="G29" s="2" t="inlineStr"/>
-      <c r="H29" s="2" t="inlineStr">
+      <c r="G28" s="2" t="inlineStr"/>
+      <c r="H28" s="2" t="inlineStr">
         <is>
           <t>96
  Hello Weihai US,
@@ -1902,39 +1858,39 @@
         </is>
       </c>
     </row>
-    <row r="30">
-      <c r="A30" s="2" t="inlineStr">
+    <row r="29">
+      <c r="A29" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B30" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C30" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D30" s="2" t="inlineStr">
+      <c r="B29" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C29" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D29" s="2" t="inlineStr">
         <is>
           <t>Thu, 2 Apr 2026 02:11:54 +0000</t>
         </is>
       </c>
-      <c r="E30" s="2" t="inlineStr">
+      <c r="E29" s="2" t="inlineStr">
         <is>
           <t>"Amazon.com" &lt;fba-noreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F30" s="2" t="inlineStr">
+      <c r="F29" s="2" t="inlineStr">
         <is>
           <t>Your FBA removal request is complete (pVfzD86piw)</t>
         </is>
       </c>
-      <c r="G30" s="2" t="inlineStr"/>
-      <c r="H30" s="2" t="inlineStr">
+      <c r="G29" s="2" t="inlineStr"/>
+      <c r="H29" s="2" t="inlineStr">
         <is>
           <t>Greetings from Amazon.com
 We thought you'd like to know that we have completed and shipped your removal
@@ -1960,39 +1916,39 @@
         </is>
       </c>
     </row>
-    <row r="31">
-      <c r="A31" s="2" t="inlineStr">
+    <row r="30">
+      <c r="A30" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B31" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C31" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D31" s="2" t="inlineStr">
+      <c r="B30" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C30" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D30" s="2" t="inlineStr">
         <is>
           <t>Tue, 31 Mar 2026 06:25:09 +0000</t>
         </is>
       </c>
-      <c r="E31" s="2" t="inlineStr">
+      <c r="E30" s="2" t="inlineStr">
         <is>
           <t>"Amazon.com" &lt;fba-noreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F31" s="2" t="inlineStr">
+      <c r="F30" s="2" t="inlineStr">
         <is>
           <t>Your FBA request is complete (CQhO1/+c38)</t>
         </is>
       </c>
-      <c r="G31" s="2" t="inlineStr"/>
-      <c r="H31" s="2" t="inlineStr">
+      <c r="G30" s="2" t="inlineStr"/>
+      <c r="H30" s="2" t="inlineStr">
         <is>
           <t>Greetings from Amazon.com
 We thought you'd like to know that we have completed your destroy request.
@@ -2012,40 +1968,40 @@
         </is>
       </c>
     </row>
-    <row r="32">
-      <c r="A32" s="2" t="inlineStr">
+    <row r="31">
+      <c r="A31" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B32" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C32" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D32" s="2" t="inlineStr">
+      <c r="B31" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C31" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D31" s="2" t="inlineStr">
         <is>
           <t>Thu, 26 Mar 2026 16:14:53 +0000</t>
         </is>
       </c>
-      <c r="E32" s="2" t="inlineStr">
+      <c r="E31" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;seller-notification@amazon.ca&gt;</t>
         </is>
       </c>
-      <c r="F32" s="2" t="inlineStr">
+      <c r="F31" s="2" t="inlineStr">
         <is>
           <t>Balance Paid on your Amazon Seller Account / Paiement du solde de
  votre compte vendeur Amazon</t>
         </is>
       </c>
-      <c r="G32" s="2" t="inlineStr"/>
-      <c r="H32" s="2" t="inlineStr">
+      <c r="G31" s="2" t="inlineStr"/>
+      <c r="H31" s="2" t="inlineStr">
         <is>
           <t>Greetings from Amazon Services.
  We have charged your credit card (Visa) for CDN$ 44.65 in an attempt to settle your Amazon.ca seller account balance.
@@ -2061,39 +2017,39 @@
         </is>
       </c>
     </row>
-    <row r="33">
-      <c r="A33" s="2" t="inlineStr">
+    <row r="32">
+      <c r="A32" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B33" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C33" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D33" s="2" t="inlineStr">
+      <c r="B32" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C32" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D32" s="2" t="inlineStr">
         <is>
           <t>Wed, 25 Mar 2026 10:55:21 +0000</t>
         </is>
       </c>
-      <c r="E33" s="2" t="inlineStr">
+      <c r="E32" s="2" t="inlineStr">
         <is>
           <t>"Amazon.com" &lt;fba-noreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F33" s="2" t="inlineStr">
+      <c r="F32" s="2" t="inlineStr">
         <is>
           <t>Your FBA request is complete (kpCypnMqWe)</t>
         </is>
       </c>
-      <c r="G33" s="2" t="inlineStr"/>
-      <c r="H33" s="2" t="inlineStr">
+      <c r="G32" s="2" t="inlineStr"/>
+      <c r="H32" s="2" t="inlineStr">
         <is>
           <t>Greetings from Amazon.com
 We thought you'd like to know that we have completed your destroy request.
@@ -2113,39 +2069,39 @@
         </is>
       </c>
     </row>
-    <row r="34">
-      <c r="A34" s="2" t="inlineStr">
+    <row r="33">
+      <c r="A33" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B34" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C34" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D34" s="2" t="inlineStr">
+      <c r="B33" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C33" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D33" s="2" t="inlineStr">
         <is>
           <t>Mon, 23 Mar 2026 18:27:53 +0000</t>
         </is>
       </c>
-      <c r="E34" s="2" t="inlineStr">
+      <c r="E33" s="2" t="inlineStr">
         <is>
           <t>"Amazon.com" &lt;fba-noreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F34" s="2" t="inlineStr">
+      <c r="F33" s="2" t="inlineStr">
         <is>
           <t>Your FBA removal request is complete (UvRxALtvwM)</t>
         </is>
       </c>
-      <c r="G34" s="2" t="inlineStr"/>
-      <c r="H34" s="2" t="inlineStr">
+      <c r="G33" s="2" t="inlineStr"/>
+      <c r="H33" s="2" t="inlineStr">
         <is>
           <t>Greetings from Amazon.com
 We thought you'd like to know that we have completed and shipped your removal
@@ -2171,39 +2127,39 @@
         </is>
       </c>
     </row>
-    <row r="35">
-      <c r="A35" s="2" t="inlineStr">
+    <row r="34">
+      <c r="A34" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B35" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C35" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D35" s="2" t="inlineStr">
+      <c r="B34" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C34" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D34" s="2" t="inlineStr">
         <is>
           <t>Mon, 23 Mar 2026 03:56:37 +0000</t>
         </is>
       </c>
-      <c r="E35" s="2" t="inlineStr">
+      <c r="E34" s="2" t="inlineStr">
         <is>
           <t>"Fulfillment by Amazon (Do not reply)" &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F35" s="2" t="inlineStr">
+      <c r="F34" s="2" t="inlineStr">
         <is>
           <t>FBA reimbursement notification</t>
         </is>
       </c>
-      <c r="G35" s="2" t="inlineStr"/>
-      <c r="H35" s="2" t="inlineStr">
+      <c r="G34" s="2" t="inlineStr"/>
+      <c r="H34" s="2" t="inlineStr">
         <is>
           <t>96
 FBA reimbursement notification
@@ -2219,39 +2175,39 @@
         </is>
       </c>
     </row>
-    <row r="36">
-      <c r="A36" s="2" t="inlineStr">
+    <row r="35">
+      <c r="A35" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B36" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C36" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D36" s="2" t="inlineStr">
+      <c r="B35" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C35" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D35" s="2" t="inlineStr">
         <is>
           <t>Sat, 21 Mar 2026 14:27:38 +0000</t>
         </is>
       </c>
-      <c r="E36" s="2" t="inlineStr">
+      <c r="E35" s="2" t="inlineStr">
         <is>
           <t>Fulfillment by Amazon Operations &lt;fba-noreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F36" s="2" t="inlineStr">
+      <c r="F35" s="2" t="inlineStr">
         <is>
           <t>Automated unfulfillable FBA inventory removal notification</t>
         </is>
       </c>
-      <c r="G36" s="2" t="inlineStr"/>
-      <c r="H36" s="2" t="inlineStr">
+      <c r="G35" s="2" t="inlineStr"/>
+      <c r="H35" s="2" t="inlineStr">
         <is>
           <t>96
  Hello Weihai US,
@@ -2272,39 +2228,39 @@
         </is>
       </c>
     </row>
-    <row r="37">
-      <c r="A37" s="2" t="inlineStr">
+    <row r="36">
+      <c r="A36" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B37" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C37" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D37" s="2" t="inlineStr">
+      <c r="B36" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C36" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D36" s="2" t="inlineStr">
         <is>
           <t>Mon, 16 Mar 2026 16:28:57 +0000</t>
         </is>
       </c>
-      <c r="E37" s="2" t="inlineStr">
+      <c r="E36" s="2" t="inlineStr">
         <is>
           <t>Amazon Multi-Channel Fulfillment Team &lt;multichannelfulfillment@supplychain.amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F37" s="2" t="inlineStr">
+      <c r="F36" s="2" t="inlineStr">
         <is>
           <t>Reminder: Please share your feedback on MCF</t>
         </is>
       </c>
-      <c r="G37" s="2" t="inlineStr"/>
-      <c r="H37" s="2" t="inlineStr">
+      <c r="G36" s="2" t="inlineStr"/>
+      <c r="H36" s="2" t="inlineStr">
         <is>
           <t>Reminder: Please share your feedback on MCF
 Dear Weihai US,
@@ -2318,39 +2274,39 @@
         </is>
       </c>
     </row>
-    <row r="38">
-      <c r="A38" s="2" t="inlineStr">
+    <row r="37">
+      <c r="A37" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B38" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C38" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D38" s="2" t="inlineStr">
+      <c r="B37" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C37" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D37" s="2" t="inlineStr">
         <is>
           <t>Tue, 7 Apr 2026 15:16:38 +0000</t>
         </is>
       </c>
-      <c r="E38" s="2" t="inlineStr">
+      <c r="E37" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;seller-notification@amazon.pl&gt;</t>
         </is>
       </c>
-      <c r="F38" s="2" t="inlineStr">
+      <c r="F37" s="2" t="inlineStr">
         <is>
           <t>Nieuregulowane saldo na koncie Amazon</t>
         </is>
       </c>
-      <c r="G38" s="2" t="inlineStr"/>
-      <c r="H38" s="2" t="inlineStr">
+      <c r="G37" s="2" t="inlineStr"/>
+      <c r="H37" s="2" t="inlineStr">
         <is>
           <t>Witamy!
  Masz na swoim koncie nieuregulowane saldo w wysokośc PLN 45.29. Obciążymy tą kwotą kartę kredytową zarejestrowaną jako metoda płatności dla Twojego konta
@@ -2364,40 +2320,40 @@
         </is>
       </c>
     </row>
-    <row r="39">
-      <c r="A39" s="2" t="inlineStr">
+    <row r="38">
+      <c r="A38" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B39" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C39" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D39" s="2" t="inlineStr">
+      <c r="B38" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C38" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D38" s="2" t="inlineStr">
         <is>
           <t>Mon, 6 Apr 2026 16:54:29 +0000</t>
         </is>
       </c>
-      <c r="E39" s="2" t="inlineStr">
+      <c r="E38" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F39" s="2" t="inlineStr">
+      <c r="F38" s="2" t="inlineStr">
         <is>
           <t>Refunds for digital services fees related to the Canadian DST will
  begin on April 15</t>
         </is>
       </c>
-      <c r="G39" s="2" t="inlineStr"/>
-      <c r="H39" s="2" t="inlineStr">
+      <c r="G38" s="2" t="inlineStr"/>
+      <c r="H38" s="2" t="inlineStr">
         <is>
           <t>96
  We’ll refund digital services fees and the taxes on those fees related to the Canadian digital services tax that we had charged from September 1, 2024, through August 15, 2025.
@@ -2414,39 +2370,39 @@
         </is>
       </c>
     </row>
-    <row r="40">
-      <c r="A40" s="2" t="inlineStr">
+    <row r="39">
+      <c r="A39" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B40" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C40" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D40" s="2" t="inlineStr">
+      <c r="B39" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C39" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D39" s="2" t="inlineStr">
         <is>
           <t>Sun, 5 Apr 2026 13:38:25 +0000</t>
         </is>
       </c>
-      <c r="E40" s="2" t="inlineStr">
+      <c r="E39" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F40" s="2" t="inlineStr">
+      <c r="F39" s="2" t="inlineStr">
         <is>
           <t>Your payment is on the way</t>
         </is>
       </c>
-      <c r="G40" s="2" t="inlineStr"/>
-      <c r="H40" s="2" t="inlineStr">
+      <c r="G39" s="2" t="inlineStr"/>
+      <c r="H39" s="2" t="inlineStr">
         <is>
           <t>96
 This title will display on mobile devices
@@ -2466,39 +2422,39 @@
         </is>
       </c>
     </row>
-    <row r="41">
-      <c r="A41" s="2" t="inlineStr">
+    <row r="40">
+      <c r="A40" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B41" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C41" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D41" s="2" t="inlineStr">
+      <c r="B40" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C40" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D40" s="2" t="inlineStr">
         <is>
           <t>Thu, 2 Apr 2026 15:38:29 +0000</t>
         </is>
       </c>
-      <c r="E41" s="2" t="inlineStr">
+      <c r="E40" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F41" s="2" t="inlineStr">
+      <c r="F40" s="2" t="inlineStr">
         <is>
           <t>Tu pago está en camino</t>
         </is>
       </c>
-      <c r="G41" s="2" t="inlineStr"/>
-      <c r="H41" s="2" t="inlineStr">
+      <c r="G40" s="2" t="inlineStr"/>
+      <c r="H40" s="2" t="inlineStr">
         <is>
           <t>96
 This title will display on mobile devices
@@ -2515,39 +2471,39 @@
         </is>
       </c>
     </row>
-    <row r="42">
-      <c r="A42" s="2" t="inlineStr">
+    <row r="41">
+      <c r="A41" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B42" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C42" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D42" s="2" t="inlineStr">
+      <c r="B41" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C41" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D41" s="2" t="inlineStr">
         <is>
           <t>Tue, 31 Mar 2026 12:51:47 +0000</t>
         </is>
       </c>
-      <c r="E42" s="2" t="inlineStr">
+      <c r="E41" s="2" t="inlineStr">
         <is>
           <t>Amazon Europe &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F42" s="2" t="inlineStr">
+      <c r="F41" s="2" t="inlineStr">
         <is>
           <t>Eco-contribution and EPR Pay on Behalf service fee charges</t>
         </is>
       </c>
-      <c r="G42" s="2" t="inlineStr"/>
-      <c r="H42" s="2" t="inlineStr">
+      <c r="G41" s="2" t="inlineStr"/>
+      <c r="H41" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">Amazon Services
  96
@@ -2570,39 +2526,39 @@
         </is>
       </c>
     </row>
-    <row r="43">
-      <c r="A43" s="2" t="inlineStr">
+    <row r="42">
+      <c r="A42" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B43" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C43" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D43" s="2" t="inlineStr">
+      <c r="B42" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C42" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D42" s="2" t="inlineStr">
         <is>
           <t>Mon, 30 Mar 2026 15:13:23 +0000</t>
         </is>
       </c>
-      <c r="E43" s="2" t="inlineStr">
+      <c r="E42" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F43" s="2" t="inlineStr">
+      <c r="F42" s="2" t="inlineStr">
         <is>
           <t>Your payment is on the way</t>
         </is>
       </c>
-      <c r="G43" s="2" t="inlineStr"/>
-      <c r="H43" s="2" t="inlineStr">
+      <c r="G42" s="2" t="inlineStr"/>
+      <c r="H42" s="2" t="inlineStr">
         <is>
           <t>96
 This title will display on mobile devices
@@ -2622,39 +2578,39 @@
         </is>
       </c>
     </row>
-    <row r="44">
-      <c r="A44" s="2" t="inlineStr">
+    <row r="43">
+      <c r="A43" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B44" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C44" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D44" s="2" t="inlineStr">
+      <c r="B43" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C43" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D43" s="2" t="inlineStr">
         <is>
           <t>Thu, 26 Mar 2026 17:33:22 +0000</t>
         </is>
       </c>
-      <c r="E44" s="2" t="inlineStr">
+      <c r="E43" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F44" s="2" t="inlineStr">
+      <c r="F43" s="2" t="inlineStr">
         <is>
           <t>View your China tax report for October - December 2025</t>
         </is>
       </c>
-      <c r="G44" s="2" t="inlineStr"/>
-      <c r="H44" s="2" t="inlineStr">
+      <c r="G43" s="2" t="inlineStr"/>
+      <c r="H43" s="2" t="inlineStr">
         <is>
           <t>96
  We’ve submitted your quarterly tax report to the Chinese tax authority. You can now download the report for reference.
@@ -2671,39 +2627,39 @@
         </is>
       </c>
     </row>
-    <row r="45">
-      <c r="A45" s="2" t="inlineStr">
+    <row r="44">
+      <c r="A44" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B45" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C45" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D45" s="2" t="inlineStr">
+      <c r="B44" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C44" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D44" s="2" t="inlineStr">
         <is>
           <t>Thu, 19 Mar 2026 15:38:31 +0000</t>
         </is>
       </c>
-      <c r="E45" s="2" t="inlineStr">
+      <c r="E44" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F45" s="2" t="inlineStr">
+      <c r="F44" s="2" t="inlineStr">
         <is>
           <t>Tu pago está en camino</t>
         </is>
       </c>
-      <c r="G45" s="2" t="inlineStr"/>
-      <c r="H45" s="2" t="inlineStr">
+      <c r="G44" s="2" t="inlineStr"/>
+      <c r="H44" s="2" t="inlineStr">
         <is>
           <t>96
 This title will display on mobile devices
@@ -2720,39 +2676,39 @@
         </is>
       </c>
     </row>
-    <row r="46">
-      <c r="A46" s="2" t="inlineStr">
+    <row r="45">
+      <c r="A45" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B46" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C46" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D46" s="2" t="inlineStr">
+      <c r="B45" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C45" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D45" s="2" t="inlineStr">
         <is>
           <t>Wed, 8 Apr 2026 10:50:30 +0000</t>
         </is>
       </c>
-      <c r="E46" s="2" t="inlineStr">
+      <c r="E45" s="2" t="inlineStr">
         <is>
           <t>Amazon Europe &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F46" s="2" t="inlineStr">
+      <c r="F45" s="2" t="inlineStr">
         <is>
           <t>EU and UK Compliance Brief</t>
         </is>
       </c>
-      <c r="G46" s="2" t="inlineStr"/>
-      <c r="H46" s="2" t="inlineStr">
+      <c r="G45" s="2" t="inlineStr"/>
+      <c r="H45" s="2" t="inlineStr">
         <is>
           <t>Amazon Europe
  96
@@ -2773,39 +2729,39 @@
         </is>
       </c>
     </row>
-    <row r="47">
-      <c r="A47" s="2" t="inlineStr">
+    <row r="46">
+      <c r="A46" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B47" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C47" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D47" s="2" t="inlineStr">
+      <c r="B46" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C46" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D46" s="2" t="inlineStr">
         <is>
           <t>Wed, 8 Apr 2026 10:38:53 +0000</t>
         </is>
       </c>
-      <c r="E47" s="2" t="inlineStr">
+      <c r="E46" s="2" t="inlineStr">
         <is>
           <t>Amazon Europe &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F47" s="2" t="inlineStr">
+      <c r="F46" s="2" t="inlineStr">
         <is>
           <t>EU and UK Compliance Brief</t>
         </is>
       </c>
-      <c r="G47" s="2" t="inlineStr"/>
-      <c r="H47" s="2" t="inlineStr">
+      <c r="G46" s="2" t="inlineStr"/>
+      <c r="H46" s="2" t="inlineStr">
         <is>
           <t>Amazon Europe
  96
@@ -2826,40 +2782,40 @@
         </is>
       </c>
     </row>
-    <row r="48">
-      <c r="A48" s="2" t="inlineStr">
+    <row r="47">
+      <c r="A47" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B48" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C48" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D48" s="2" t="inlineStr">
+      <c r="B47" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C47" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D47" s="2" t="inlineStr">
         <is>
           <t>Wed, 8 Apr 2026 10:23:33 +0000</t>
         </is>
       </c>
-      <c r="E48" s="2" t="inlineStr">
+      <c r="E47" s="2" t="inlineStr">
         <is>
           <t>The Amazon Europe team &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F48" s="2" t="inlineStr">
+      <c r="F47" s="2" t="inlineStr">
         <is>
           <t>VAT Calculation Services will calculate VAT by shipment as of June
  1</t>
         </is>
       </c>
-      <c r="G48" s="2" t="inlineStr"/>
-      <c r="H48" s="2" t="inlineStr">
+      <c r="G47" s="2" t="inlineStr"/>
+      <c r="H47" s="2" t="inlineStr">
         <is>
           <t>96
  New tax calculation method ensures compliance with European e-invoicing mandates.
@@ -2875,39 +2831,39 @@
         </is>
       </c>
     </row>
-    <row r="49">
-      <c r="A49" s="2" t="inlineStr">
+    <row r="48">
+      <c r="A48" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B49" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C49" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D49" s="2" t="inlineStr">
+      <c r="B48" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C48" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D48" s="2" t="inlineStr">
         <is>
           <t>Thu, 2 Apr 2026 04:56:03 +0000</t>
         </is>
       </c>
-      <c r="E49" s="2" t="inlineStr">
+      <c r="E48" s="2" t="inlineStr">
         <is>
           <t>"ppwr-cn-seller-compliance@amazon.com" &lt;ppwr-cn-seller-compliance@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F49" s="2" t="inlineStr">
+      <c r="F48" s="2" t="inlineStr">
         <is>
           <t>RE:[CASE 12309992722] 需要采取行动：请向亚马逊提交您的EPR包装法注册号</t>
         </is>
       </c>
-      <c r="G49" s="2" t="inlineStr"/>
-      <c r="H49" s="2" t="inlineStr">
+      <c r="G48" s="2" t="inlineStr"/>
+      <c r="H48" s="2" t="inlineStr">
         <is>
           <t>【请勿回复】
 尊敬的销售合作伙伴，
@@ -2930,39 +2886,39 @@
         </is>
       </c>
     </row>
-    <row r="50">
-      <c r="A50" s="2" t="inlineStr">
+    <row r="49">
+      <c r="A49" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B50" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C50" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D50" s="2" t="inlineStr">
+      <c r="B49" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C49" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D49" s="2" t="inlineStr">
         <is>
           <t>Thu, 2 Apr 2026 02:19:17 +0000</t>
         </is>
       </c>
-      <c r="E50" s="2" t="inlineStr">
+      <c r="E49" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F50" s="2" t="inlineStr">
+      <c r="F49" s="2" t="inlineStr">
         <is>
           <t>Submit product safety documentation to reactivate listings</t>
         </is>
       </c>
-      <c r="G50" s="2" t="inlineStr"/>
-      <c r="H50" s="2" t="inlineStr">
+      <c r="G49" s="2" t="inlineStr"/>
+      <c r="H49" s="2" t="inlineStr">
         <is>
           <t>96
  Submit product safety documentation to reactivate listings
@@ -2980,39 +2936,39 @@
         </is>
       </c>
     </row>
-    <row r="51">
-      <c r="A51" s="2" t="inlineStr">
+    <row r="50">
+      <c r="A50" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B51" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C51" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D51" s="2" t="inlineStr">
+      <c r="B50" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C50" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D50" s="2" t="inlineStr">
         <is>
           <t>Thu, 2 Apr 2026 02:18:50 +0000</t>
         </is>
       </c>
-      <c r="E51" s="2" t="inlineStr">
+      <c r="E50" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F51" s="2" t="inlineStr">
+      <c r="F50" s="2" t="inlineStr">
         <is>
           <t>Submit product safety documentation to reactivate listings</t>
         </is>
       </c>
-      <c r="G51" s="2" t="inlineStr"/>
-      <c r="H51" s="2" t="inlineStr">
+      <c r="G50" s="2" t="inlineStr"/>
+      <c r="H50" s="2" t="inlineStr">
         <is>
           <t>96
  Submit product safety documentation to reactivate listings
@@ -3030,39 +2986,39 @@
         </is>
       </c>
     </row>
-    <row r="52">
-      <c r="A52" s="2" t="inlineStr">
+    <row r="51">
+      <c r="A51" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B52" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C52" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D52" s="2" t="inlineStr">
+      <c r="B51" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C51" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D51" s="2" t="inlineStr">
         <is>
           <t>Tue, 31 Mar 2026 21:25:34 +0000</t>
         </is>
       </c>
-      <c r="E52" s="2" t="inlineStr">
+      <c r="E51" s="2" t="inlineStr">
         <is>
           <t>"Amazon Seller Central notifications (Do not reply)" &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F52" s="2" t="inlineStr">
+      <c r="F51" s="2" t="inlineStr">
         <is>
           <t>Address compliance requirements for your listings</t>
         </is>
       </c>
-      <c r="G52" s="2" t="inlineStr"/>
-      <c r="H52" s="2" t="inlineStr">
+      <c r="G51" s="2" t="inlineStr"/>
+      <c r="H51" s="2" t="inlineStr">
         <is>
           <t>96
 Action required: Important information about your product listings
@@ -3082,39 +3038,39 @@
         </is>
       </c>
     </row>
-    <row r="53">
-      <c r="A53" s="2" t="inlineStr">
+    <row r="52">
+      <c r="A52" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B53" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C53" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D53" s="2" t="inlineStr">
+      <c r="B52" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C52" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D52" s="2" t="inlineStr">
         <is>
           <t>Mon, 30 Mar 2026 07:07:52 +0000</t>
         </is>
       </c>
-      <c r="E53" s="2" t="inlineStr">
+      <c r="E52" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F53" s="2" t="inlineStr">
+      <c r="F52" s="2" t="inlineStr">
         <is>
           <t>Submit product safety documentation to reactivate listings</t>
         </is>
       </c>
-      <c r="G53" s="2" t="inlineStr"/>
-      <c r="H53" s="2" t="inlineStr">
+      <c r="G52" s="2" t="inlineStr"/>
+      <c r="H52" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">96
  Submit product safety documentation to reactivate listings
@@ -3132,39 +3088,39 @@
         </is>
       </c>
     </row>
-    <row r="54">
-      <c r="A54" s="2" t="inlineStr">
+    <row r="53">
+      <c r="A53" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B54" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C54" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D54" s="2" t="inlineStr">
+      <c r="B53" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C53" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D53" s="2" t="inlineStr">
         <is>
           <t>Sat, 28 Mar 2026 13:21:45 +0000</t>
         </is>
       </c>
-      <c r="E54" s="2" t="inlineStr">
+      <c r="E53" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F54" s="2" t="inlineStr">
+      <c r="F53" s="2" t="inlineStr">
         <is>
           <t>Submit product safety documentation to reactivate listings</t>
         </is>
       </c>
-      <c r="G54" s="2" t="inlineStr"/>
-      <c r="H54" s="2" t="inlineStr">
+      <c r="G53" s="2" t="inlineStr"/>
+      <c r="H53" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">96
  Submit product safety documentation to reactivate listings
@@ -3182,39 +3138,39 @@
         </is>
       </c>
     </row>
-    <row r="55">
-      <c r="A55" s="2" t="inlineStr">
+    <row r="54">
+      <c r="A54" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B55" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C55" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D55" s="2" t="inlineStr">
+      <c r="B54" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C54" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D54" s="2" t="inlineStr">
         <is>
           <t>Sat, 28 Mar 2026 13:01:16 +0000</t>
         </is>
       </c>
-      <c r="E55" s="2" t="inlineStr">
+      <c r="E54" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F55" s="2" t="inlineStr">
+      <c r="F54" s="2" t="inlineStr">
         <is>
           <t>Submit product safety documentation to reactivate listings</t>
         </is>
       </c>
-      <c r="G55" s="2" t="inlineStr"/>
-      <c r="H55" s="2" t="inlineStr">
+      <c r="G54" s="2" t="inlineStr"/>
+      <c r="H54" s="2" t="inlineStr">
         <is>
           <t>96
  Submit product safety documentation to reactivate listings
@@ -3232,39 +3188,39 @@
         </is>
       </c>
     </row>
-    <row r="56">
-      <c r="A56" s="2" t="inlineStr">
+    <row r="55">
+      <c r="A55" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B56" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C56" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D56" s="2" t="inlineStr">
+      <c r="B55" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C55" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D55" s="2" t="inlineStr">
         <is>
           <t>Fri, 27 Mar 2026 14:37:14 +0000</t>
         </is>
       </c>
-      <c r="E56" s="2" t="inlineStr">
+      <c r="E55" s="2" t="inlineStr">
         <is>
           <t>Sell with Amazon &lt;no-reply@sell.amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F56" s="2" t="inlineStr">
+      <c r="F55" s="2" t="inlineStr">
         <is>
           <t>Live Q&amp;A on customer feedback with experienced sellers</t>
         </is>
       </c>
-      <c r="G56" s="2" t="inlineStr"/>
-      <c r="H56" s="2" t="inlineStr">
+      <c r="G55" s="2" t="inlineStr"/>
+      <c r="H55" s="2" t="inlineStr">
         <is>
           <t>[Amazon logo](https://go.amazonsellerservices.com/e/229492/-ref--spc-em-na-frm-20260324/7z2bw3r/6577485148/h/BOm7kDreq_ieAJ8P9nkJWZ402nkYiTu_wgkPAn3aZYs)
 Connect with sellers experienced in customer feedback
@@ -3279,39 +3235,39 @@
         </is>
       </c>
     </row>
-    <row r="57">
-      <c r="A57" s="2" t="inlineStr">
+    <row r="56">
+      <c r="A56" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B57" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C57" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D57" s="2" t="inlineStr">
+      <c r="B56" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C56" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D56" s="2" t="inlineStr">
         <is>
           <t>Fri, 27 Mar 2026 13:18:53 +0000</t>
         </is>
       </c>
-      <c r="E57" s="2" t="inlineStr">
+      <c r="E56" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F57" s="2" t="inlineStr">
+      <c r="F56" s="2" t="inlineStr">
         <is>
           <t>Submit product safety documentation to reactivate listings</t>
         </is>
       </c>
-      <c r="G57" s="2" t="inlineStr"/>
-      <c r="H57" s="2" t="inlineStr">
+      <c r="G56" s="2" t="inlineStr"/>
+      <c r="H56" s="2" t="inlineStr">
         <is>
           <t>96
  Submit product safety documentation to reactivate listings
@@ -3329,39 +3285,39 @@
         </is>
       </c>
     </row>
-    <row r="58">
-      <c r="A58" s="2" t="inlineStr">
+    <row r="57">
+      <c r="A57" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B58" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C58" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D58" s="2" t="inlineStr">
+      <c r="B57" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C57" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D57" s="2" t="inlineStr">
         <is>
           <t>Fri, 27 Mar 2026 13:13:28 +0000</t>
         </is>
       </c>
-      <c r="E58" s="2" t="inlineStr">
+      <c r="E57" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F58" s="2" t="inlineStr">
+      <c r="F57" s="2" t="inlineStr">
         <is>
           <t>Submit product safety documentation to reactivate listings</t>
         </is>
       </c>
-      <c r="G58" s="2" t="inlineStr"/>
-      <c r="H58" s="2" t="inlineStr">
+      <c r="G57" s="2" t="inlineStr"/>
+      <c r="H57" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">96
  Submit product safety documentation to reactivate listings
@@ -3379,39 +3335,39 @@
         </is>
       </c>
     </row>
-    <row r="59">
-      <c r="A59" s="2" t="inlineStr">
+    <row r="58">
+      <c r="A58" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B59" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C59" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D59" s="2" t="inlineStr">
+      <c r="B58" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C58" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D58" s="2" t="inlineStr">
         <is>
           <t>Fri, 27 Mar 2026 12:51:52 +0000</t>
         </is>
       </c>
-      <c r="E59" s="2" t="inlineStr">
+      <c r="E58" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F59" s="2" t="inlineStr">
+      <c r="F58" s="2" t="inlineStr">
         <is>
           <t>Submit product safety documentation to reactivate listings</t>
         </is>
       </c>
-      <c r="G59" s="2" t="inlineStr"/>
-      <c r="H59" s="2" t="inlineStr">
+      <c r="G58" s="2" t="inlineStr"/>
+      <c r="H58" s="2" t="inlineStr">
         <is>
           <t>96
  Submit product safety documentation to reactivate listings
@@ -3429,39 +3385,39 @@
         </is>
       </c>
     </row>
-    <row r="60">
-      <c r="A60" s="2" t="inlineStr">
+    <row r="59">
+      <c r="A59" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B60" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C60" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D60" s="2" t="inlineStr">
+      <c r="B59" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C59" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D59" s="2" t="inlineStr">
         <is>
           <t>Fri, 27 Mar 2026 08:16:10 +0000</t>
         </is>
       </c>
-      <c r="E60" s="2" t="inlineStr">
+      <c r="E59" s="2" t="inlineStr">
         <is>
           <t>"fba-3p-buyability-improvement-us@amazon.com" &lt;fba-3p-buyability-improvement-us@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F60" s="2" t="inlineStr">
+      <c r="F59" s="2" t="inlineStr">
         <is>
           <t>Action Required: Website Suppressed ASINs</t>
         </is>
       </c>
-      <c r="G60" s="2" t="inlineStr"/>
-      <c r="H60" s="2" t="inlineStr">
+      <c r="G59" s="2" t="inlineStr"/>
+      <c r="H59" s="2" t="inlineStr">
         <is>
           <t>Dear Seller,
 We are part of Buyability Audit team at Amazon. The Buyability program aims to identify and eliminate root causes leading to Buyability drop-off. We are contacting you to let you know that you could be missing out on sales opportunities due to the suppression of some of your ASINs.
@@ -3476,39 +3432,39 @@
         </is>
       </c>
     </row>
-    <row r="61">
-      <c r="A61" s="2" t="inlineStr">
+    <row r="60">
+      <c r="A60" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B61" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C61" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D61" s="2" t="inlineStr">
+      <c r="B60" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C60" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D60" s="2" t="inlineStr">
         <is>
           <t>Thu, 26 Mar 2026 15:17:29 +0000</t>
         </is>
       </c>
-      <c r="E61" s="2" t="inlineStr">
+      <c r="E60" s="2" t="inlineStr">
         <is>
           <t>"fba-3p-buyability-improvement-us@amazon.com" &lt;fba-3p-buyability-improvement-us@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F61" s="2" t="inlineStr">
+      <c r="F60" s="2" t="inlineStr">
         <is>
           <t>Action Required: Website Suppressed ASINs</t>
         </is>
       </c>
-      <c r="G61" s="2" t="inlineStr"/>
-      <c r="H61" s="2" t="inlineStr">
+      <c r="G60" s="2" t="inlineStr"/>
+      <c r="H60" s="2" t="inlineStr">
         <is>
           <t>Dear Seller,
 We are part of Buyability Audit team at Amazon. The Buyability program aims to identify and eliminate root causes leading to Buyability drop-off. We are contacting you to let you know that you could be missing out on sales opportunities due to the suppression of some of your ASINs.
@@ -3523,39 +3479,39 @@
         </is>
       </c>
     </row>
-    <row r="62">
-      <c r="A62" s="2" t="inlineStr">
+    <row r="61">
+      <c r="A61" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B62" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C62" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D62" s="2" t="inlineStr">
+      <c r="B61" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C61" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D61" s="2" t="inlineStr">
         <is>
           <t>Tue, 24 Mar 2026 14:28:08 +0000</t>
         </is>
       </c>
-      <c r="E62" s="2" t="inlineStr">
+      <c r="E61" s="2" t="inlineStr">
         <is>
           <t>"fba-3p-buyability-improvement-us@amazon.com" &lt;fba-3p-buyability-improvement-us@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F62" s="2" t="inlineStr">
+      <c r="F61" s="2" t="inlineStr">
         <is>
           <t>Action Required: Website Suppressed ASINs</t>
         </is>
       </c>
-      <c r="G62" s="2" t="inlineStr"/>
-      <c r="H62" s="2" t="inlineStr">
+      <c r="G61" s="2" t="inlineStr"/>
+      <c r="H61" s="2" t="inlineStr">
         <is>
           <t>Dear Seller,
 We are part of Buyability Audit team at Amazon. The Buyability program aims to identify and eliminate root causes leading to Buyability drop-off. We are contacting you to let you know that you could be missing out on sales opportunities due to the suppression of some of your ASINs.
@@ -3570,39 +3526,39 @@
         </is>
       </c>
     </row>
-    <row r="63">
-      <c r="A63" s="2" t="inlineStr">
+    <row r="62">
+      <c r="A62" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B63" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C63" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D63" s="2" t="inlineStr">
+      <c r="B62" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C62" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D62" s="2" t="inlineStr">
         <is>
           <t>Tue, 24 Mar 2026 04:25:09 +0000</t>
         </is>
       </c>
-      <c r="E63" s="2" t="inlineStr">
+      <c r="E62" s="2" t="inlineStr">
         <is>
           <t>Fulfillment by Amazon Operations &lt;fba-noreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F63" s="2" t="inlineStr">
+      <c r="F62" s="2" t="inlineStr">
         <is>
           <t>Your Amazon.com Inventory - Action Required</t>
         </is>
       </c>
-      <c r="G63" s="2" t="inlineStr"/>
-      <c r="H63" s="2" t="inlineStr">
+      <c r="G62" s="2" t="inlineStr"/>
+      <c r="H62" s="2" t="inlineStr">
         <is>
           <t>Dear Weihai US,
 We have recently restricted listings for the product(s) listed below on Amazon.com.
@@ -3621,40 +3577,40 @@
         </is>
       </c>
     </row>
-    <row r="64">
-      <c r="A64" s="2" t="inlineStr">
+    <row r="63">
+      <c r="A63" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B64" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C64" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D64" s="2" t="inlineStr">
+      <c r="B63" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C63" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D63" s="2" t="inlineStr">
         <is>
           <t>Mon, 23 Mar 2026 11:52:08 +0000</t>
         </is>
       </c>
-      <c r="E64" s="2" t="inlineStr">
+      <c r="E63" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F64" s="2" t="inlineStr">
+      <c r="F63" s="2" t="inlineStr">
         <is>
           <t>Submit UK import details by 21/05/2026 to avoid shipping
  restrictions</t>
         </is>
       </c>
-      <c r="G64" s="2" t="inlineStr"/>
-      <c r="H64" s="2" t="inlineStr">
+      <c r="G63" s="2" t="inlineStr"/>
+      <c r="H63" s="2" t="inlineStr">
         <is>
           <t>96
  Submit UK import details by 21/05/2026 to avoid shipping restrictions
@@ -3673,39 +3629,39 @@
         </is>
       </c>
     </row>
-    <row r="65">
-      <c r="A65" s="2" t="inlineStr">
+    <row r="64">
+      <c r="A64" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B65" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C65" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D65" s="2" t="inlineStr">
+      <c r="B64" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C64" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D64" s="2" t="inlineStr">
         <is>
           <t>Mon, 23 Mar 2026 07:21:52 +0000</t>
         </is>
       </c>
-      <c r="E65" s="2" t="inlineStr">
+      <c r="E64" s="2" t="inlineStr">
         <is>
           <t>Amazon Europe &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F65" s="2" t="inlineStr">
+      <c r="F64" s="2" t="inlineStr">
         <is>
           <t>Add products to Amazon.nl for Pan EU eligibility</t>
         </is>
       </c>
-      <c r="G65" s="2" t="inlineStr"/>
-      <c r="H65" s="2" t="inlineStr">
+      <c r="G64" s="2" t="inlineStr"/>
+      <c r="H64" s="2" t="inlineStr">
         <is>
           <t>Add products to Amazon.nl for Pan EU eligibility 96
  Complete Pan EU enrollment: Add NL products now
@@ -3715,39 +3671,39 @@
         </is>
       </c>
     </row>
-    <row r="66">
-      <c r="A66" s="2" t="inlineStr">
+    <row r="65">
+      <c r="A65" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B66" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C66" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D66" s="2" t="inlineStr">
+      <c r="B65" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C65" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D65" s="2" t="inlineStr">
         <is>
           <t>Sat, 21 Mar 2026 21:58:00 +0000</t>
         </is>
       </c>
-      <c r="E66" s="2" t="inlineStr">
+      <c r="E65" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F66" s="2" t="inlineStr">
+      <c r="F65" s="2" t="inlineStr">
         <is>
           <t>Submit product safety documentation to reactivate listings</t>
         </is>
       </c>
-      <c r="G66" s="2" t="inlineStr"/>
-      <c r="H66" s="2" t="inlineStr">
+      <c r="G65" s="2" t="inlineStr"/>
+      <c r="H65" s="2" t="inlineStr">
         <is>
           <t>96
  Submit product safety documentation to reactivate listings
@@ -3765,39 +3721,39 @@
         </is>
       </c>
     </row>
-    <row r="67">
-      <c r="A67" s="2" t="inlineStr">
+    <row r="66">
+      <c r="A66" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B67" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C67" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D67" s="2" t="inlineStr">
+      <c r="B66" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C66" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D66" s="2" t="inlineStr">
         <is>
           <t>Fri, 20 Mar 2026 21:10:27 +0000</t>
         </is>
       </c>
-      <c r="E67" s="2" t="inlineStr">
+      <c r="E66" s="2" t="inlineStr">
         <is>
           <t>"fba-3p-buyability-improvement-ca@amazon.com" &lt;fba-3p-buyability-improvement-ca@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F67" s="2" t="inlineStr">
+      <c r="F66" s="2" t="inlineStr">
         <is>
           <t>Action Required: Website Suppressed ASINs</t>
         </is>
       </c>
-      <c r="G67" s="2" t="inlineStr"/>
-      <c r="H67" s="2" t="inlineStr">
+      <c r="G66" s="2" t="inlineStr"/>
+      <c r="H66" s="2" t="inlineStr">
         <is>
           <t>Dear Seller,
 We are contacting you to let you know that you could be missing out on sales opportunities because of your incomplete listings.
@@ -3810,6 +3766,50 @@
  https://sellercentral.amazon.ca/performance/account/health/compliance-request
 If you need further help, please raise a case via contact us. - https://sellercentral.amazon.ca/cu/contact-us?ref=xx_ContactUs_xxxx_helphub
 If you are not the correct point of contact, please re-direct this email to the correct point of contact</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="2" t="inlineStr">
+        <is>
+          <t>法务/侵权类</t>
+        </is>
+      </c>
+      <c r="B67" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C67" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D67" s="2" t="inlineStr">
+        <is>
+          <t>Thu, 9 Apr 2026 08:46:52 +0000</t>
+        </is>
+      </c>
+      <c r="E67" s="2" t="inlineStr">
+        <is>
+          <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
+        </is>
+      </c>
+      <c r="F67" s="2" t="inlineStr">
+        <is>
+          <t>Addebito delle tariffe di rimozione e per reimpiego quando le unità vengono elaborate</t>
+        </is>
+      </c>
+      <c r="G67" s="2" t="inlineStr"/>
+      <c r="H67" s="2" t="inlineStr">
+        <is>
+          <t>96
+ Le tariffe per gli ordini di rimozione e di reimpiego di inventario di Logistica di Amazon verranno ora addebitate per unità ogni volta che un'unità viene rimossa o destinata ad altro uso.
+ Buongiorno,
+ a partire dal 1° maggio 2026, le tariffe per gli ordini di rimozione e di reimpiego di inventario di Logistica di Amazon verranno addebitate per unità nel momento in cui ciascuna unità viene rimossa o destinata ad altro uso. Questo aggiornamento è in linea con gli standard del settore e offre una maggiore visibilità sulle attività di rimozione e reimpiego di inventario.
+ Questa modifica riguarda solo i casi in cui ti viene addebitato il costo. Le tariffe per gli ordini di rimozione e di reimpiego di inventario rimangono invariate. In precedenza, queste tariffe venivano addebitate una volta completato l'intero ordine di rimozione o di reimpiego di inventario.
+ A questo proposito, non è richiesto alcun intervento da parte tua. Questa modifica verrà applicata automaticamente ai nuovi ordini di rimozione e di reimpiego di inventario creati a partire dal 1° maggio.
+ Per consultare i costi di rimozione e reimpiego di inventario a livello di spedizione e verificare quando le unità veng</t>
         </is>
       </c>
     </row>

--- a/important_mails_2026-04-16.xlsx
+++ b/important_mails_2026-04-16.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H132"/>
+  <dimension ref="A1:H133"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -485,12 +485,12 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>店铺绩效类</t>
+          <t>付款/资金类</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>last7</t>
+          <t>today</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr">
@@ -500,21 +500,167 @@
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>Tue, 14 Apr 2026 04:59:05 +0000</t>
+          <t>Thu, 16 Apr 2026 15:38:30 +0000</t>
         </is>
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>"Amazon.com" &lt;fba-noreply@amazon.com&gt;</t>
+          <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>Your FBA request is complete (26041219YV)</t>
+          <t>Tu pago está en camino</t>
         </is>
       </c>
       <c r="G2" s="2" t="inlineStr"/>
       <c r="H2" s="2" t="inlineStr">
+        <is>
+          <t>96
+This title will display on mobile devices
+ ¡Enhorabuena! El pago está de camino y llegará pronto.
+ El pago está en camino
+Enhorabuena, Weihai EU. Tu pago está en camino y te llegará en un plazo de tres a cinco días.
+El 04/16/26 15:38 WEST, iniciamos una transferencia a tu método de pago (cuenta bancaria terminado en 229) por un importe de €
+ 1,26.
+ Si el importe es inferior a lo esperado, ten en cuenta las siguientes preguntas:
+ ¿Tienes saldo no disponible en tu cuenta de vendedor? Puede que hayamos reservado algo de dinero para posibles devoluciones, reclamaciones o reversiones de cargo de clientes. En este caso, el saldo de cierre de tu informe de pagos te mostrará el saldo no disponible en reserva.
+ ¿Cubren tus ventas las tarifas de Amazon y las devoluciones del periodo de liquidación? El importe del pago refleja las ventas que has hecho y las tarifas de venta aplicadas tanto a dichas ventas como a cualquier promoción o servicio que hayas utilizado. Te recomendamos que revises tu informe de pagos en "Informes" de Seller Central para conocer el saldo de cierre.
+Para más información sobre los informes de pagos en Seller Central, visita nuestro curso oficial.
+Te deseamos un éxit</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>产品链接/合规类</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="inlineStr">
+        <is>
+          <t>today</t>
+        </is>
+      </c>
+      <c r="C3" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D3" s="2" t="inlineStr">
+        <is>
+          <t>Thu, 16 Apr 2026 17:53:23 +0000</t>
+        </is>
+      </c>
+      <c r="E3" s="2" t="inlineStr">
+        <is>
+          <t>Fulfillment by Amazon Operations &lt;fba-noreply@amazon.com&gt;</t>
+        </is>
+      </c>
+      <c r="F3" s="2" t="inlineStr">
+        <is>
+          <t>Your Amazon.com Inventory - Action Required</t>
+        </is>
+      </c>
+      <c r="G3" s="2" t="inlineStr"/>
+      <c r="H3" s="2" t="inlineStr">
+        <is>
+          <t>Dear Weihai US,
+We have recently restricted listings for the product(s) listed below on Amazon.com.
+Please initiate a removal request for the ASIN(s) referenced below to have your inventory sent to a location of your choosing. If this inventory is not removed within 30 days of this notification (by 05/15/2026), we may dispose of it in accordance with FBA policies.
+Thank you for your attention to this matter.
+Regards,
+Product Safety Team
+Amazon.com
+www.amazon.com
+Please note: this e-mail was sent from a notification-only address that cannot accept incoming e-mail. Please do not reply to this message.
+Affected Product(s):
+B0FCDRNTT8
+Was this email helpful?
+ https://sellercentral.amazon.com/gp/satisfaction/survey-form.html?ie=UTF8&amp;HMDName=NotificationBusEmailHMD&amp;customAttribute1Value=RESTRICTED_LISTING_PRODUCTS_REMOVAL_REQUEST
+SPC-USAmazon-1864773927693727</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>法务/侵权类</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
+          <t>today</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>Thu, 16 Apr 2026 15:10:49 +0000</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>[Formal Notice – Immediate Action Required] Review and certify your business information within 10 days to avoid account deactivation</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr"/>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>96
+ Hello Weihai US,
+ Under the US INFORM Consumers Act, you are required to keep certain business information provided to Amazon current, including your name, address, phone number, email address, bank account information, and Tax ID number. You are also required to electronically certify to Amazon at least once per year that either you have provided any changes to your information or there have been no changes to this information.
+ Review your account information and complete your electronic certification by following the instructions below to avoid disruption to your selling account. If you do not certify your information within 10 days of this notice, your account will be at risk of account deactivation, as required by the law.
+ (Please disregard this notice if you have already certified your information and received an acknowledgment notice.)
+ How do I certify my information and avoid account deactivation?
+ Go to the INFORM Act Notice and Certification step in your ( Account Health page ).
+ Follow the instructions on the page to review the required information, update it if necessary, and click the “Certify” button to certify that it is up-to-date.
+ Please note that only the p</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>店铺绩效类</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="inlineStr">
+        <is>
+          <t>last7</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>Tue, 14 Apr 2026 04:59:05 +0000</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>"Amazon.com" &lt;fba-noreply@amazon.com&gt;</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>Your FBA request is complete (26041219YV)</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr"/>
+      <c r="H5" s="2" t="inlineStr">
         <is>
           <t>Greetings from Amazon.com
 We thought you'd like to know that we have completed your destroy request.
@@ -534,39 +680,39 @@
         </is>
       </c>
     </row>
-    <row r="3">
-      <c r="A3" s="2" t="inlineStr">
+    <row r="6">
+      <c r="A6" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B3" s="2" t="inlineStr">
+      <c r="B6" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C3" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D3" s="2" t="inlineStr">
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
         <is>
           <t>Mon, 13 Apr 2026 16:26:54 +0000</t>
         </is>
       </c>
-      <c r="E3" s="2" t="inlineStr">
+      <c r="E6" s="2" t="inlineStr">
         <is>
           <t>Amazon Payments Europe &lt;amazon_te@amazon.fr&gt;</t>
         </is>
       </c>
-      <c r="F3" s="2" t="inlineStr">
+      <c r="F6" s="2" t="inlineStr">
         <is>
           <t>Paiement du solde de votre compte de paiement Vendre sur Amazon</t>
         </is>
       </c>
-      <c r="G3" s="2" t="inlineStr"/>
-      <c r="H3" s="2" t="inlineStr">
+      <c r="G6" s="2" t="inlineStr"/>
+      <c r="H6" s="2" t="inlineStr">
         <is>
           <t>Cher vendeur,
  Nous avons débité votre carte bancaire (Visa) pour un montant de 242,36 EUR pour le règlement du solde de votre compte de paiement Vendre sur Amazon.
@@ -578,39 +724,39 @@
         </is>
       </c>
     </row>
-    <row r="4">
-      <c r="A4" s="2" t="inlineStr">
+    <row r="7">
+      <c r="A7" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B4" s="2" t="inlineStr">
+      <c r="B7" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C4" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
         <is>
           <t>Mon, 13 Apr 2026 15:24:52 +0000</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="E7" s="2" t="inlineStr">
         <is>
           <t>Amazon Payments Europe &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
+      <c r="F7" s="2" t="inlineStr">
         <is>
           <t>Negative balance adjustment across your Selling on Amazon accounts</t>
         </is>
       </c>
-      <c r="G4" s="2" t="inlineStr"/>
-      <c r="H4" s="2" t="inlineStr">
+      <c r="G7" s="2" t="inlineStr"/>
+      <c r="H7" s="2" t="inlineStr">
         <is>
           <t>96
 This title will display on mobile devices
@@ -633,39 +779,39 @@
         </is>
       </c>
     </row>
-    <row r="5">
-      <c r="A5" s="2" t="inlineStr">
+    <row r="8">
+      <c r="A8" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B5" s="2" t="inlineStr">
+      <c r="B8" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C5" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
         <is>
           <t>Sat, 11 Apr 2026 15:29:23 +0000</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
+      <c r="E8" s="2" t="inlineStr">
         <is>
           <t>Amazon Payments Europe &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F5" s="2" t="inlineStr">
+      <c r="F8" s="2" t="inlineStr">
         <is>
           <t>Rettifica del saldo negativo nei tuoi account</t>
         </is>
       </c>
-      <c r="G5" s="2" t="inlineStr"/>
-      <c r="H5" s="2" t="inlineStr">
+      <c r="G8" s="2" t="inlineStr"/>
+      <c r="H8" s="2" t="inlineStr">
         <is>
           <t>96
 This title will display on mobile devices
@@ -689,86 +835,39 @@
         </is>
       </c>
     </row>
-    <row r="6">
-      <c r="A6" s="2" t="inlineStr">
-        <is>
-          <t>付款/资金类</t>
-        </is>
-      </c>
-      <c r="B6" s="2" t="inlineStr">
+    <row r="9">
+      <c r="A9" s="2" t="inlineStr">
+        <is>
+          <t>产品链接/合规类</t>
+        </is>
+      </c>
+      <c r="B9" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C6" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>Thu, 9 Apr 2026 14:28:35 +0000</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>Amazon Payments UK Limited &lt;seller-notification@amazon.com&gt;</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>Balance Paid on Your Selling on Amazon payment account</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr"/>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>Dear Seller,
- We have charged your (Visa) credit card for 62.05 in an attempt to settle your account balance.
- Please note that the amount charged to your credit card may be less than the total amount you owe due to a credit limit imposed by your bank. In this case, we may continue to attempt charging your card until the remaining balance in your Amazon Selling on Amazon payment account is paid in full.
- You can also use the Make a Payment feature to repay the balance you owe. For details, refer “Making a Payment” in Seller Central Help.
- To view your payment activity anytime, please log in to your account and refer the Payments Report page.
- Thank you for selling on Amazon.
- Amazon Payments UK Limited
-Amazon Payments UK Limited, a private company limited by shares, is a company registered in England and Wales (registration number 11049457; VAT number: GB295 7604 60) with its registered office at 1 Principal Place, Worship St, London, EC2A 2FA, United Kingdom. Amazon Payments UK Limited is authorised by the UK Financial Conduct Authority under the Payment Services Regulations 2017 (reference number 799814) for the provision of payment services.
- Was this e-mail helpful?
- SPC-EUAmaz</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="2" t="inlineStr">
-        <is>
-          <t>产品链接/合规类</t>
-        </is>
-      </c>
-      <c r="B7" s="2" t="inlineStr">
-        <is>
-          <t>last7</t>
-        </is>
-      </c>
-      <c r="C7" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
         <is>
           <t>Tue, 14 Apr 2026 09:10:03 +0000</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
+      <c r="E9" s="2" t="inlineStr">
         <is>
           <t>Fulfilment by Amazon Operations &lt;fba-noreply@amazon.lu&gt;</t>
         </is>
       </c>
-      <c r="F7" s="2" t="inlineStr">
+      <c r="F9" s="2" t="inlineStr">
         <is>
           <t>Your Amazon-Fulfilled Inventory - Action Required</t>
         </is>
       </c>
-      <c r="G7" s="2" t="inlineStr"/>
-      <c r="H7" s="2" t="inlineStr">
+      <c r="G9" s="2" t="inlineStr"/>
+      <c r="H9" s="2" t="inlineStr">
         <is>
           <t>Dear Seller,
 You recently received a notice concerning the removal of your listing(s) for the product(s) below due to a safety recall.
@@ -784,39 +883,39 @@
         </is>
       </c>
     </row>
-    <row r="8">
-      <c r="A8" s="2" t="inlineStr">
+    <row r="10">
+      <c r="A10" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B8" s="2" t="inlineStr">
+      <c r="B10" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C8" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
         <is>
           <t>Tue, 14 Apr 2026 07:35:31 +0000</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
+      <c r="E10" s="2" t="inlineStr">
         <is>
           <t>Amazon Europe &lt;no-reply@sell.amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F8" s="2" t="inlineStr">
+      <c r="F10" s="2" t="inlineStr">
         <is>
           <t>Seller Assistant now available in the UK</t>
         </is>
       </c>
-      <c r="G8" s="2" t="inlineStr"/>
-      <c r="H8" s="2" t="inlineStr">
+      <c r="G10" s="2" t="inlineStr"/>
+      <c r="H10" s="2" t="inlineStr">
         <is>
           <t>Seller Assistant now available in the UK
 [Amazon logo](https://go.amazonsellerservices.com/e/229492/-ld-EMUSSMX-PD25/7z2r9lq/6605548725/h/3xRPn8Yyq31Jz0Gqi8FK51O58vBJkaDT5nhLB1ousbA)
@@ -828,39 +927,39 @@
         </is>
       </c>
     </row>
-    <row r="9">
-      <c r="A9" s="2" t="inlineStr">
+    <row r="11">
+      <c r="A11" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B9" s="2" t="inlineStr">
+      <c r="B11" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C9" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
         <is>
           <t>Tue, 14 Apr 2026 06:23:28 +0000</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="E11" s="2" t="inlineStr">
         <is>
           <t>Fulfillment by Amazon Operations &lt;fba-noreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
+      <c r="F11" s="2" t="inlineStr">
         <is>
           <t>Your Amazon.com Inventory</t>
         </is>
       </c>
-      <c r="G9" s="2" t="inlineStr"/>
-      <c r="H9" s="2" t="inlineStr">
+      <c r="G11" s="2" t="inlineStr"/>
+      <c r="H11" s="2" t="inlineStr">
         <is>
           <t>Dear Weihai US,
 You recently received a notice about the removal of your listing(s) for the product(s) listed below.
@@ -880,39 +979,39 @@
         </is>
       </c>
     </row>
-    <row r="10">
-      <c r="A10" s="2" t="inlineStr">
+    <row r="12">
+      <c r="A12" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B10" s="2" t="inlineStr">
+      <c r="B12" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C10" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
         <is>
           <t>Sun, 12 Apr 2026 09:09:25 +0000</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
+      <c r="E12" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F10" s="2" t="inlineStr">
+      <c r="F12" s="2" t="inlineStr">
         <is>
           <t>Submit product safety documentation to reactivate listings</t>
         </is>
       </c>
-      <c r="G10" s="2" t="inlineStr"/>
-      <c r="H10" s="2" t="inlineStr">
+      <c r="G12" s="2" t="inlineStr"/>
+      <c r="H12" s="2" t="inlineStr">
         <is>
           <t>96
  Submit product safety documentation to reactivate listings
@@ -930,40 +1029,40 @@
         </is>
       </c>
     </row>
-    <row r="11">
-      <c r="A11" s="2" t="inlineStr">
+    <row r="13">
+      <c r="A13" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B11" s="2" t="inlineStr">
+      <c r="B13" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C11" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
         <is>
           <t>Fri, 10 Apr 2026 15:28:03 +0000</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
+      <c r="E13" s="2" t="inlineStr">
         <is>
           <t>"cscompliance-docreview-seller@amazon.com" &lt;cscompliance-docreview-seller@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F11" s="2" t="inlineStr">
+      <c r="F13" s="2" t="inlineStr">
         <is>
           <t>SELLER: A192R36HNXVJ38, ASIN: B0FCDRNTT8, MARKETPLACE: 1 - CSC -
  DOC REVIEW</t>
         </is>
       </c>
-      <c r="G11" s="2" t="inlineStr"/>
-      <c r="H11" s="2" t="inlineStr">
+      <c r="G13" s="2" t="inlineStr"/>
+      <c r="H13" s="2" t="inlineStr">
         <is>
           <t>Do not reply back to this e-mail!
 Hello,
@@ -981,91 +1080,39 @@
         </is>
       </c>
     </row>
-    <row r="12">
-      <c r="A12" s="2" t="inlineStr">
-        <is>
-          <t>产品链接/合规类</t>
-        </is>
-      </c>
-      <c r="B12" s="2" t="inlineStr">
+    <row r="14">
+      <c r="A14" s="2" t="inlineStr">
+        <is>
+          <t>法务/侵权类</t>
+        </is>
+      </c>
+      <c r="B14" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C12" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>Thu, 9 Apr 2026 12:03:53 +0000</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>Reactivate your EU listings - GPSR compliance required</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr"/>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">96
- Reactivate your EU listings - GPSR compliance required
- Hello Weihai EU,
- Some of your listings have been deactivated from our European Union (EU) stores due to missing compliance information. This action does not impact your account health.
- You can find examples of your deactivated listings at the bottom of this email, and the full list on your Account Health page. Review the affected listings and next steps to meet General Product Safety Regulation (GPSR) requirements below.
- Submit compliance information
- Submit compliance information
- How do I reactivate my listings?
- To reactivate your listings, provide the required GPSR compliance information by following the instructions below:
--
- Go to your Account Health page .
-- Select 'Add filters' and check 'Listing removed' in the "Filter by action taken" column.
-- Click 'Submit' next to the deactivated listing and follow the instructions provided.
-- Follow the steps on Suppressed listings to resolve any outstanding listing issues. Existing issues prevent listings from being reactivated, even if you’ve fulfilled all compliance requirements.
- Note: If you’ve recently submitted information on your Account Health page, and no longer </t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="2" t="inlineStr">
-        <is>
-          <t>法务/侵权类</t>
-        </is>
-      </c>
-      <c r="B13" s="2" t="inlineStr">
-        <is>
-          <t>last7</t>
-        </is>
-      </c>
-      <c r="C13" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
         <is>
           <t>Tue, 14 Apr 2026 17:59:02 +0000</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
+      <c r="E14" s="2" t="inlineStr">
         <is>
           <t>Amazon Verkaeuferservice &lt;merch.service05@amazon.de&gt;</t>
         </is>
       </c>
-      <c r="F13" s="2" t="inlineStr">
+      <c r="F14" s="2" t="inlineStr">
         <is>
           <t>RE:[CASE 12354633592] 其他账户问题</t>
         </is>
       </c>
-      <c r="G13" s="2" t="inlineStr"/>
-      <c r="H13" s="2" t="inlineStr">
+      <c r="G14" s="2" t="inlineStr"/>
+      <c r="H14" s="2" t="inlineStr">
         <is>
           <t>尊敬的销售伙伴：
 您好！
@@ -1084,40 +1131,40 @@
         </is>
       </c>
     </row>
-    <row r="14">
-      <c r="A14" s="2" t="inlineStr">
+    <row r="15">
+      <c r="A15" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B14" s="2" t="inlineStr">
+      <c r="B15" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C14" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
         <is>
           <t>Tue, 14 Apr 2026 17:22:14 +0000</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
+      <c r="E15" s="2" t="inlineStr">
         <is>
           <t>Amazon Product Support Team &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F14" s="2" t="inlineStr">
+      <c r="F15" s="2" t="inlineStr">
         <is>
           <t>Reduce Returns &amp; Boost Customer Satisfaction - Enrol in Amazon
  Product Support</t>
         </is>
       </c>
-      <c r="G14" s="2" t="inlineStr"/>
-      <c r="H14" s="2" t="inlineStr">
+      <c r="G15" s="2" t="inlineStr"/>
+      <c r="H15" s="2" t="inlineStr">
         <is>
           <t>96
  Enrol now into Amazon Product Support !
@@ -1131,40 +1178,40 @@
         </is>
       </c>
     </row>
-    <row r="15">
-      <c r="A15" s="2" t="inlineStr">
+    <row r="16">
+      <c r="A16" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B15" s="2" t="inlineStr">
+      <c r="B16" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C15" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="C16" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
         <is>
           <t>Fri, 10 Apr 2026 13:44:27 +0000</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="E16" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
+      <c r="F16" s="2" t="inlineStr">
         <is>
           <t>Reactiva tus listings en la UE: se requiere el cumplimiento del
  Reglamento relativo a la seguridad general de los productos</t>
         </is>
       </c>
-      <c r="G15" s="2" t="inlineStr"/>
-      <c r="H15" s="2" t="inlineStr">
+      <c r="G16" s="2" t="inlineStr"/>
+      <c r="H16" s="2" t="inlineStr">
         <is>
           <t>96
  Reactiva tus listings en la UE: se requiere el cumplimiento del Reglamento relativo a la seguridad general de los productos
@@ -1182,39 +1229,39 @@
         </is>
       </c>
     </row>
-    <row r="16">
-      <c r="A16" s="2" t="inlineStr">
+    <row r="17">
+      <c r="A17" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B16" s="2" t="inlineStr">
+      <c r="B17" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C16" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="C17" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
         <is>
           <t>Fri, 10 Apr 2026 01:52:13 +0000</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
+      <c r="E17" s="2" t="inlineStr">
         <is>
           <t>Justin Bangina &lt;justin.bangina@vergleich.org&gt;</t>
         </is>
       </c>
-      <c r="F16" s="2" t="inlineStr">
+      <c r="F17" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">Re: 🏆 German quality seal for "Roaxkois Schwimmgurt für Pool" </t>
         </is>
       </c>
-      <c r="G16" s="2" t="inlineStr"/>
-      <c r="H16" s="2" t="inlineStr">
+      <c r="G17" s="2" t="inlineStr"/>
+      <c r="H17" s="2" t="inlineStr">
         <is>
           <t>Hello from Berlin,
 Just a short follow-up regarding the [Vergleich.org](http://Vergleich.org)
@@ -1247,57 +1294,10 @@
         </is>
       </c>
     </row>
-    <row r="17">
-      <c r="A17" s="2" t="inlineStr">
-        <is>
-          <t>法务/侵权类</t>
-        </is>
-      </c>
-      <c r="B17" s="2" t="inlineStr">
-        <is>
-          <t>last7</t>
-        </is>
-      </c>
-      <c r="C17" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D17" s="2" t="inlineStr">
-        <is>
-          <t>Thu, 9 Apr 2026 17:17:52 +0000</t>
-        </is>
-      </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>The Amazon Services team &lt;donotreply@amazon.com&gt;</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>Introducing Global Warehousing &amp; Distribution</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr"/>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>96
- Store inventory at origin in China with lower costs and faster speeds.
- Hello,
- Starting April 9, 2026, you can store your inventory in bulk at a lower cost in our new Global Warehousing &amp; Distribution (GWD) facility in Shenzhen, China, and seamlessly replenish to our US fulfillment network when needed.
- By using GWD in Shenzhen, you can:
-- Reduce storage costs by up to 45% compared to US Amazon Warehousing and Distribution (AWD).
-- Get inventory to US fulfillment centers up to seven days faster when paired with Amazon Global Logistics (AGL).
-- Maintain consistently healthy inventory levels through reliable, automated cross-border replenishment.
-- Choose your management style of either AI-powered automated replenishment or manual control while we handle the entire cross-border logistics process.
-- Streamline your supply chain of shipping, customs clearance, and delivery to our fulfillment centers all through a single, integrated solution. GWD is the first step in our Next Generation of Global Selling vision — where you list once, bring your inventory to the warehouse at origin, and sell it globally from day one. This vision transforms cross-border commerce: you focus on buildin</t>
-        </is>
-      </c>
-    </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>法务/侵权类</t>
+          <t>货件/库存类</t>
         </is>
       </c>
       <c r="B18" s="2" t="inlineStr">
@@ -1312,215 +1312,21 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>Thu, 9 Apr 2026 16:27:24 +0000</t>
+          <t>Tue, 14 Apr 2026 18:58:06 +0000</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>donotreply@amazon.com</t>
+          <t>Fulfilment by Amazon &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>Your Amazon.ca Fulfillment by Amazon Merchant Invoice for 3/2026 (Votre Facture Expédié Par Amazon Amazon.ca pour le mois de 3/2026)</t>
+          <t>Create FBA removal order by 2026-04-23</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr"/>
       <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>Dear Shen zhen shi wei hai zhong xin ke ji you xian,
-We are writing to inform you that your electronic Fulfillment by Amazon Merchant Invoice for the month of 3/2026 is now available in your Seller Central Account.
-To access your invoice, go to your Seller Central Account &gt; Reports &gt; Tax Document Library &gt; Seller Fee Tax Invoices.
-In your Seller Central account, you will be able to view, download or print your invoice.
-If you have any questions, please contact Seller Support.
-Best regards,
-Amazon.ca
- Monsieur/Madame Shen zhen shi wei hai zhong xin ke ji you xian,
-Nous vous écrivons pour vous informer que votre Facture Expédié Par Amazon pour le mois de 3/2026 est maintenant disponible dans votre compte Seller Central.
-Pour accéder à votre facture, rendez-vous sur votre compte Seller Central et veuillez accéder à la page Rapports &gt; Bibliothèque d'informations fiscales &gt; Factures des frais du vendeur.
-Dans votre compte Seller Central, vous pourrez afficher, télécharger ou imprimer votre facture.
-Pour toute question, contactez le Support Vendeur.
-Cordialement,
-Amazon.ca</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="2" t="inlineStr">
-        <is>
-          <t>法务/侵权类</t>
-        </is>
-      </c>
-      <c r="B19" s="2" t="inlineStr">
-        <is>
-          <t>last7</t>
-        </is>
-      </c>
-      <c r="C19" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D19" s="2" t="inlineStr">
-        <is>
-          <t>Thu, 9 Apr 2026 11:49:51 +0000</t>
-        </is>
-      </c>
-      <c r="E19" s="2" t="inlineStr">
-        <is>
-          <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
-        </is>
-      </c>
-      <c r="F19" s="2" t="inlineStr">
-        <is>
-          <t>Riattivare le offerte nell'UE - Richiesta la conformità al Regolamento sulla sicurezza generale dei prodotti</t>
-        </is>
-      </c>
-      <c r="G19" s="2" t="inlineStr"/>
-      <c r="H19" s="2" t="inlineStr">
-        <is>
-          <t>96
- Riattivare le offerte nell'UE - Richiesta la conformità al Regolamento sulla sicurezza generale dei prodotti
- Gentile Weihai EU,
- Alcune delle tue offerte sono state disattivate nei nostri negozi dell'Unione europea a causa della mancanza di informazioni relative alla conformità. Questa azione non avrà alcun impatto sullo stato del tuo account.
- Puoi trovare esempi delle tue offerte disattivate in fondo a questa e-mail e l'elenco completo nella pagina Stato dell'account. Rivedi le offerte interessate e i passaggi successivi per soddisfare i requisiti del Regolamento sulla sicurezza generale dei prodotti riportati di seguito.
- Inviare le informazioni sulla conformità
- Inviare le informazioni sulla conformità
- Come faccio a riattivare le mie offerte?
- Per riattivare le offerte, fornisci le informazioni richieste relative alla conformità al regolamento sulla sicurezza generale dei prodotti seguendo le istruzioni riportate di seguito:
--
- Vai alla pagina Stato dell'account .
-- Seleziona "Aggiungi filtri" e quindi "Offerta rimossa" nella colonna "Filtra per azione intrapresa".
-- Clicca su "Invia" accanto all'offerta disattivata e segui le istruzioni fornite.
-- Segui la procedura indi</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="2" t="inlineStr">
-        <is>
-          <t>法务/侵权类</t>
-        </is>
-      </c>
-      <c r="B20" s="2" t="inlineStr">
-        <is>
-          <t>last7</t>
-        </is>
-      </c>
-      <c r="C20" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D20" s="2" t="inlineStr">
-        <is>
-          <t>Thu, 9 Apr 2026 10:53:45 +0000</t>
-        </is>
-      </c>
-      <c r="E20" s="2" t="inlineStr">
-        <is>
-          <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
-        </is>
-      </c>
-      <c r="F20" s="2" t="inlineStr">
-        <is>
-          <t>Las tarifas por puesta de inventario a disposición de Amazon y retirada de Logística de Amazon se cobrarán a medida que se procesen las unidades</t>
-        </is>
-      </c>
-      <c r="G20" s="2" t="inlineStr"/>
-      <c r="H20" s="2" t="inlineStr">
-        <is>
-          <t>96
- Las tarifas por retirada y puesta de inventario a disposición de Amazon de Logística de Amazon se cobrarán ahora por unidad en el momento en que cada unidad se retire o se ponga a nuestra disposición.
- Hola:
- Con entrada en vigor el 1 de mayo de 2026, las tarifas por puesta de inventario a disposición de Amazon y retirada de Logística de Amazon se cobrarán por unidad en el momento en que cada unidad se retire o se ponga a nuestra disposición. Con esta actualización, seguimos los estándares del sector y te proporcionamos más visibilidad sobre tus actividades de retirada y puesta de inventario a nuestra disposición.
- Este cambio sólo afecta al momento en que se te cobra. No hay cambios en las tarifas por retirada y puesta de inventario a disposición de Amazon. Antes, estas tarifas se cobraban una vez que se completaba toda la solicitud de retirada o puesta de inventario a disposición de Amazon.
- No es necesario que hagas nada. Este cambio se aplicará automáticamente a las nuevas solicitudes de retirada y puesta de inventario a disposición de Amazon creadas a partir del 1 de mayo.
- Para consultar los cargos por envío de las retiradas y puestas de inventario a nuestra disposición y</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="2" t="inlineStr">
-        <is>
-          <t>法务/侵权类</t>
-        </is>
-      </c>
-      <c r="B21" s="2" t="inlineStr">
-        <is>
-          <t>last7</t>
-        </is>
-      </c>
-      <c r="C21" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D21" s="2" t="inlineStr">
-        <is>
-          <t>Thu, 9 Apr 2026 09:19:33 +0000</t>
-        </is>
-      </c>
-      <c r="E21" s="2" t="inlineStr">
-        <is>
-          <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
-        </is>
-      </c>
-      <c r="F21" s="2" t="inlineStr">
-        <is>
-          <t>Opłaty za usunięcie i likwidację zapasów FBA naliczane podczas przetwarzania jednostek</t>
-        </is>
-      </c>
-      <c r="G21" s="2" t="inlineStr"/>
-      <c r="H21" s="2" t="inlineStr">
-        <is>
-          <t>96
- Opłaty za wycofanie i usunięcie zapasów w ramach FBA będą teraz pobierane od każdej jednostki w momencie jej wycofania lub usunięcia.
- Dzień dobry,
- od 1 maja 2026 r. opłaty za wycofanie i usunięcie w ramach usługi Realizacja przez Amazon (FBA) będą pobierane od każdej jednostki w momencie jej wycofania lub usunięcia. Aktualizacja jest zgodna ze standardami branżowymi i zapewnia większą przejrzystość działań związanych z wycofywaniem i usuwaniem zapasów.
- Zmiana dotyczy wyłącznie momentu pobrania opłaty. Stawki opłat za wycofanie i usunięcie zapasów pozostają bez zmian. Wcześniej opłaty były pobierane po zakończeniu realizacji całego zlecenia wycofania zapasów lub zlecenia usunięcia zapasów.
- Nie musisz podejmować żadnych działań. Zmiana zostanie automatycznie zastosowana do nowych zleceń wycofania zapasów i zleceń usunięcia zapasów utworzonych od 1 maja.
- Aby sprawdzić opłaty na poziomie przesyłki dotyczące wycofania i usunięcia zapasów oraz terminy wycofywania jednostek, przejdź na kartę Transakcje .
- Więcej informacji znajdziesz na stronie Aktualizacje opłat za wycofanie i usunięcie zapasów w ramach FBA .
- Zespół Amazon Europe
- Zgłoś problem z tym e-mailem
- Jeśli masz pytani</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="2" t="inlineStr">
-        <is>
-          <t>货件/库存类</t>
-        </is>
-      </c>
-      <c r="B22" s="2" t="inlineStr">
-        <is>
-          <t>last7</t>
-        </is>
-      </c>
-      <c r="C22" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D22" s="2" t="inlineStr">
-        <is>
-          <t>Tue, 14 Apr 2026 18:58:06 +0000</t>
-        </is>
-      </c>
-      <c r="E22" s="2" t="inlineStr">
-        <is>
-          <t>Fulfilment by Amazon &lt;donotreply@amazon.com&gt;</t>
-        </is>
-      </c>
-      <c r="F22" s="2" t="inlineStr">
-        <is>
-          <t>Create FBA removal order by 2026-04-23</t>
-        </is>
-      </c>
-      <c r="G22" s="2" t="inlineStr"/>
-      <c r="H22" s="2" t="inlineStr">
         <is>
           <t>96
 Automated removals of unfulfillable inventory
@@ -1541,39 +1347,39 @@
         </is>
       </c>
     </row>
-    <row r="23">
-      <c r="A23" s="2" t="inlineStr">
+    <row r="19">
+      <c r="A19" s="2" t="inlineStr">
         <is>
           <t>货件/库存类</t>
         </is>
       </c>
-      <c r="B23" s="2" t="inlineStr">
+      <c r="B19" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C23" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D23" s="2" t="inlineStr">
+      <c r="C19" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
         <is>
           <t>Tue, 14 Apr 2026 18:27:29 +0000</t>
         </is>
       </c>
-      <c r="E23" s="2" t="inlineStr">
+      <c r="E19" s="2" t="inlineStr">
         <is>
           <t>Fulfilment by Amazon &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F23" s="2" t="inlineStr">
+      <c r="F19" s="2" t="inlineStr">
         <is>
           <t>Disposal order created for unsellable FBA inventory</t>
         </is>
       </c>
-      <c r="G23" s="2" t="inlineStr"/>
-      <c r="H23" s="2" t="inlineStr">
+      <c r="G19" s="2" t="inlineStr"/>
+      <c r="H19" s="2" t="inlineStr">
         <is>
           <t>96
 Automated Removals of Unfulfillable Inventory
@@ -1596,39 +1402,39 @@
         </is>
       </c>
     </row>
-    <row r="24">
-      <c r="A24" s="2" t="inlineStr">
+    <row r="20">
+      <c r="A20" s="2" t="inlineStr">
         <is>
           <t>其他风险类</t>
         </is>
       </c>
-      <c r="B24" s="2" t="inlineStr">
+      <c r="B20" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C24" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D24" s="2" t="inlineStr">
+      <c r="C20" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
         <is>
           <t>Fri, 10 Apr 2026 14:20:37 +0000</t>
         </is>
       </c>
-      <c r="E24" s="2" t="inlineStr">
+      <c r="E20" s="2" t="inlineStr">
         <is>
           <t>Amazon Europe &lt;noreply@sell.amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F24" s="2" t="inlineStr">
+      <c r="F20" s="2" t="inlineStr">
         <is>
           <t>Get discounts up to €500 per shipment by expanding to Europe!</t>
         </is>
       </c>
-      <c r="G24" s="2" t="inlineStr"/>
-      <c r="H24" s="2" t="inlineStr">
+      <c r="G20" s="2" t="inlineStr"/>
+      <c r="H20" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">[Amazon logo](https://go.amazonsellerservices.com/e/229492/-logo/7z2qvdy/6598918207/h/oQJ3hcZAc232rnIjbHrMLH2dvtBVfEq_dAzSA60S8Es)
 C2S2 PCP Pallet Limited Time Promotion
@@ -1644,142 +1450,39 @@
         </is>
       </c>
     </row>
-    <row r="25">
-      <c r="A25" s="2" t="inlineStr">
-        <is>
-          <t>其他风险类</t>
-        </is>
-      </c>
-      <c r="B25" s="2" t="inlineStr">
-        <is>
-          <t>last7</t>
-        </is>
-      </c>
-      <c r="C25" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D25" s="2" t="inlineStr">
-        <is>
-          <t>Thu, 9 Apr 2026 11:27:28 +0000</t>
-        </is>
-      </c>
-      <c r="E25" s="2" t="inlineStr">
-        <is>
-          <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
-        </is>
-      </c>
-      <c r="F25" s="2" t="inlineStr">
-        <is>
-          <t>FBA removal and disposal fees to be charged as units are processed</t>
-        </is>
-      </c>
-      <c r="G25" s="2" t="inlineStr"/>
-      <c r="H25" s="2" t="inlineStr">
-        <is>
-          <t>96
- FBA removal and disposal fees will now be charged on a per-unit basis at the time each unit is removed or disposed of.
- Hello,
- Effective May 1, 2026, Fulfillment by Amazon (FBA) removal and disposal fees will be charged on a per-unit basis at the time each unit is removed or disposed of. This update is in line with industry standards and gives you more visibility into your removal and disposal activities.
- This change only affects when you are charged. The fee rates for removal and disposal fees remain unchanged. Previously, these fees were charged once the entire removal or disposal order was completed.
- No action is required from you. This change will apply automatically to new removal and disposal orders created on or after May 1.
- To review your removal and disposal shipment level charges and when units are removed, go to Transaction view .
- For more information, go to FBA Removal and Disposal fee updates .
- The Amazon Europe team
- Report an issue with this email
- If you have any questions visit: Seller Central
- To change your email preferences visit: Notification Preferences
- Copyright 2026 Amazon, Inc, or its affiliates. All rights reserved.
- Amazon EU S.à r.l.
-38 avenue</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" s="2" t="inlineStr">
-        <is>
-          <t>其他风险类</t>
-        </is>
-      </c>
-      <c r="B26" s="2" t="inlineStr">
-        <is>
-          <t>last7</t>
-        </is>
-      </c>
-      <c r="C26" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D26" s="2" t="inlineStr">
-        <is>
-          <t>Thu, 9 Apr 2026 10:52:42 +0000</t>
-        </is>
-      </c>
-      <c r="E26" s="2" t="inlineStr">
-        <is>
-          <t>Amazon Services Europe &lt;donotreply@amazon.com&gt;</t>
-        </is>
-      </c>
-      <c r="F26" s="2" t="inlineStr">
-        <is>
-          <t>FBA removal and disposal fees to be charged as units are processed</t>
-        </is>
-      </c>
-      <c r="G26" s="2" t="inlineStr"/>
-      <c r="H26" s="2" t="inlineStr">
-        <is>
-          <t>96
- FBA removal and disposal fees will now be charged on a per-unit basis at the time that each unit is removed or disposed of.
- Hello,
- Effective as of May 1, 2026, Fulfilment by Amazon (FBA) removal and disposal fees will be charged on a per-unit basis at the time that each unit is removed or disposed of. This update is in line with industry standards and gives you more visibility into your removal and disposal activities.
- This change only affects when you are charged. The fee rates for removal and disposal fees remain unchanged. Previously, these fees were charged once the entire removal or disposal order was completed.
- No action is required from you. This change will apply automatically to new removal and disposal orders created on or after May 1.
- To review your removal and disposal shipment-level charges and when units are removed, go to Transaction view .
- For more information, go to FBA removal and disposal fee updates .
- The Amazon Europe team
- Report an issue with this email
- If you have any questions visit: Seller Central
- To change your email preferences visit: Notification Preferences
- Copyright 2026 Amazon, Inc, or its affiliates. All rights reserved.
- Amazon EU S.à</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" s="2" t="inlineStr">
+    <row r="21">
+      <c r="A21" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B27" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C27" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D27" s="2" t="inlineStr">
+      <c r="B21" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C21" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
         <is>
           <t>Wed, 8 Apr 2026 02:11:54 +0000</t>
         </is>
       </c>
-      <c r="E27" s="2" t="inlineStr">
+      <c r="E21" s="2" t="inlineStr">
         <is>
           <t>"Amazon.com" &lt;fba-noreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F27" s="2" t="inlineStr">
+      <c r="F21" s="2" t="inlineStr">
         <is>
           <t>Your FBA removal request is complete (W4mGNrNTVu)</t>
         </is>
       </c>
-      <c r="G27" s="2" t="inlineStr"/>
-      <c r="H27" s="2" t="inlineStr">
+      <c r="G21" s="2" t="inlineStr"/>
+      <c r="H21" s="2" t="inlineStr">
         <is>
           <t>Greetings from Amazon.com
 We thought you'd like to know that we have completed and shipped your removal
@@ -1805,39 +1508,39 @@
         </is>
       </c>
     </row>
-    <row r="28">
-      <c r="A28" s="2" t="inlineStr">
+    <row r="22">
+      <c r="A22" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B28" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C28" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D28" s="2" t="inlineStr">
+      <c r="B22" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C22" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
         <is>
           <t>Mon, 6 Apr 2026 15:50:12 +0000</t>
         </is>
       </c>
-      <c r="E28" s="2" t="inlineStr">
+      <c r="E22" s="2" t="inlineStr">
         <is>
           <t>Fulfillment by Amazon Operations &lt;fba-noreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F28" s="2" t="inlineStr">
+      <c r="F22" s="2" t="inlineStr">
         <is>
           <t>Automated unfulfillable FBA inventory removal notification</t>
         </is>
       </c>
-      <c r="G28" s="2" t="inlineStr"/>
-      <c r="H28" s="2" t="inlineStr">
+      <c r="G22" s="2" t="inlineStr"/>
+      <c r="H22" s="2" t="inlineStr">
         <is>
           <t>96
  Hello Weihai US,
@@ -1858,39 +1561,39 @@
         </is>
       </c>
     </row>
-    <row r="29">
-      <c r="A29" s="2" t="inlineStr">
+    <row r="23">
+      <c r="A23" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B29" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C29" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D29" s="2" t="inlineStr">
+      <c r="B23" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C23" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
         <is>
           <t>Thu, 2 Apr 2026 02:11:54 +0000</t>
         </is>
       </c>
-      <c r="E29" s="2" t="inlineStr">
+      <c r="E23" s="2" t="inlineStr">
         <is>
           <t>"Amazon.com" &lt;fba-noreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F29" s="2" t="inlineStr">
+      <c r="F23" s="2" t="inlineStr">
         <is>
           <t>Your FBA removal request is complete (pVfzD86piw)</t>
         </is>
       </c>
-      <c r="G29" s="2" t="inlineStr"/>
-      <c r="H29" s="2" t="inlineStr">
+      <c r="G23" s="2" t="inlineStr"/>
+      <c r="H23" s="2" t="inlineStr">
         <is>
           <t>Greetings from Amazon.com
 We thought you'd like to know that we have completed and shipped your removal
@@ -1916,39 +1619,39 @@
         </is>
       </c>
     </row>
-    <row r="30">
-      <c r="A30" s="2" t="inlineStr">
+    <row r="24">
+      <c r="A24" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B30" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C30" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D30" s="2" t="inlineStr">
+      <c r="B24" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C24" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
         <is>
           <t>Tue, 31 Mar 2026 06:25:09 +0000</t>
         </is>
       </c>
-      <c r="E30" s="2" t="inlineStr">
+      <c r="E24" s="2" t="inlineStr">
         <is>
           <t>"Amazon.com" &lt;fba-noreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F30" s="2" t="inlineStr">
+      <c r="F24" s="2" t="inlineStr">
         <is>
           <t>Your FBA request is complete (CQhO1/+c38)</t>
         </is>
       </c>
-      <c r="G30" s="2" t="inlineStr"/>
-      <c r="H30" s="2" t="inlineStr">
+      <c r="G24" s="2" t="inlineStr"/>
+      <c r="H24" s="2" t="inlineStr">
         <is>
           <t>Greetings from Amazon.com
 We thought you'd like to know that we have completed your destroy request.
@@ -1968,40 +1671,40 @@
         </is>
       </c>
     </row>
-    <row r="31">
-      <c r="A31" s="2" t="inlineStr">
+    <row r="25">
+      <c r="A25" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B31" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C31" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D31" s="2" t="inlineStr">
+      <c r="B25" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C25" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D25" s="2" t="inlineStr">
         <is>
           <t>Thu, 26 Mar 2026 16:14:53 +0000</t>
         </is>
       </c>
-      <c r="E31" s="2" t="inlineStr">
+      <c r="E25" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;seller-notification@amazon.ca&gt;</t>
         </is>
       </c>
-      <c r="F31" s="2" t="inlineStr">
+      <c r="F25" s="2" t="inlineStr">
         <is>
           <t>Balance Paid on your Amazon Seller Account / Paiement du solde de
  votre compte vendeur Amazon</t>
         </is>
       </c>
-      <c r="G31" s="2" t="inlineStr"/>
-      <c r="H31" s="2" t="inlineStr">
+      <c r="G25" s="2" t="inlineStr"/>
+      <c r="H25" s="2" t="inlineStr">
         <is>
           <t>Greetings from Amazon Services.
  We have charged your credit card (Visa) for CDN$ 44.65 in an attempt to settle your Amazon.ca seller account balance.
@@ -2017,39 +1720,39 @@
         </is>
       </c>
     </row>
-    <row r="32">
-      <c r="A32" s="2" t="inlineStr">
+    <row r="26">
+      <c r="A26" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B32" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C32" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D32" s="2" t="inlineStr">
+      <c r="B26" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C26" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D26" s="2" t="inlineStr">
         <is>
           <t>Wed, 25 Mar 2026 10:55:21 +0000</t>
         </is>
       </c>
-      <c r="E32" s="2" t="inlineStr">
+      <c r="E26" s="2" t="inlineStr">
         <is>
           <t>"Amazon.com" &lt;fba-noreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F32" s="2" t="inlineStr">
+      <c r="F26" s="2" t="inlineStr">
         <is>
           <t>Your FBA request is complete (kpCypnMqWe)</t>
         </is>
       </c>
-      <c r="G32" s="2" t="inlineStr"/>
-      <c r="H32" s="2" t="inlineStr">
+      <c r="G26" s="2" t="inlineStr"/>
+      <c r="H26" s="2" t="inlineStr">
         <is>
           <t>Greetings from Amazon.com
 We thought you'd like to know that we have completed your destroy request.
@@ -2069,39 +1772,39 @@
         </is>
       </c>
     </row>
-    <row r="33">
-      <c r="A33" s="2" t="inlineStr">
+    <row r="27">
+      <c r="A27" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B33" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C33" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D33" s="2" t="inlineStr">
+      <c r="B27" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C27" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D27" s="2" t="inlineStr">
         <is>
           <t>Mon, 23 Mar 2026 18:27:53 +0000</t>
         </is>
       </c>
-      <c r="E33" s="2" t="inlineStr">
+      <c r="E27" s="2" t="inlineStr">
         <is>
           <t>"Amazon.com" &lt;fba-noreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F33" s="2" t="inlineStr">
+      <c r="F27" s="2" t="inlineStr">
         <is>
           <t>Your FBA removal request is complete (UvRxALtvwM)</t>
         </is>
       </c>
-      <c r="G33" s="2" t="inlineStr"/>
-      <c r="H33" s="2" t="inlineStr">
+      <c r="G27" s="2" t="inlineStr"/>
+      <c r="H27" s="2" t="inlineStr">
         <is>
           <t>Greetings from Amazon.com
 We thought you'd like to know that we have completed and shipped your removal
@@ -2127,39 +1830,39 @@
         </is>
       </c>
     </row>
-    <row r="34">
-      <c r="A34" s="2" t="inlineStr">
+    <row r="28">
+      <c r="A28" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B34" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C34" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D34" s="2" t="inlineStr">
+      <c r="B28" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C28" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D28" s="2" t="inlineStr">
         <is>
           <t>Mon, 23 Mar 2026 03:56:37 +0000</t>
         </is>
       </c>
-      <c r="E34" s="2" t="inlineStr">
+      <c r="E28" s="2" t="inlineStr">
         <is>
           <t>"Fulfillment by Amazon (Do not reply)" &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F34" s="2" t="inlineStr">
+      <c r="F28" s="2" t="inlineStr">
         <is>
           <t>FBA reimbursement notification</t>
         </is>
       </c>
-      <c r="G34" s="2" t="inlineStr"/>
-      <c r="H34" s="2" t="inlineStr">
+      <c r="G28" s="2" t="inlineStr"/>
+      <c r="H28" s="2" t="inlineStr">
         <is>
           <t>96
 FBA reimbursement notification
@@ -2175,39 +1878,39 @@
         </is>
       </c>
     </row>
-    <row r="35">
-      <c r="A35" s="2" t="inlineStr">
+    <row r="29">
+      <c r="A29" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B35" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C35" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D35" s="2" t="inlineStr">
+      <c r="B29" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C29" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D29" s="2" t="inlineStr">
         <is>
           <t>Sat, 21 Mar 2026 14:27:38 +0000</t>
         </is>
       </c>
-      <c r="E35" s="2" t="inlineStr">
+      <c r="E29" s="2" t="inlineStr">
         <is>
           <t>Fulfillment by Amazon Operations &lt;fba-noreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F35" s="2" t="inlineStr">
+      <c r="F29" s="2" t="inlineStr">
         <is>
           <t>Automated unfulfillable FBA inventory removal notification</t>
         </is>
       </c>
-      <c r="G35" s="2" t="inlineStr"/>
-      <c r="H35" s="2" t="inlineStr">
+      <c r="G29" s="2" t="inlineStr"/>
+      <c r="H29" s="2" t="inlineStr">
         <is>
           <t>96
  Hello Weihai US,
@@ -2228,85 +1931,86 @@
         </is>
       </c>
     </row>
-    <row r="36">
-      <c r="A36" s="2" t="inlineStr">
-        <is>
-          <t>店铺绩效类</t>
-        </is>
-      </c>
-      <c r="B36" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C36" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D36" s="2" t="inlineStr">
-        <is>
-          <t>Mon, 16 Mar 2026 16:28:57 +0000</t>
-        </is>
-      </c>
-      <c r="E36" s="2" t="inlineStr">
-        <is>
-          <t>Amazon Multi-Channel Fulfillment Team &lt;multichannelfulfillment@supplychain.amazon.com&gt;</t>
-        </is>
-      </c>
-      <c r="F36" s="2" t="inlineStr">
-        <is>
-          <t>Reminder: Please share your feedback on MCF</t>
-        </is>
-      </c>
-      <c r="G36" s="2" t="inlineStr"/>
-      <c r="H36" s="2" t="inlineStr">
-        <is>
-          <t>Reminder: Please share your feedback on MCF
-Dear Weihai US,
-As a valued Multi-Channel Fulfillment (MCF) managed customer, we are interested in learning about your program feedback including new features that may benefit your business. This may help us understand how we can better meet your business needs and continue to improve the customer experience. Please complete this survey no later than March 19.
-(button)  Click here to complete survey  https://amazonexteu.qualtrics.com/jfe/form/SV_et9BAqtoDGCsCB8?Q_CHL=gl&amp;amp;Q_DL=EMD_Z45pcIhoS9Jgg2Y_et9BAqtoDGCsCB8_CGC_gVqjuURBQB4eTq0&amp;amp;_g_=g
-This submission form is unique to your Seller account and can only be submitted once.
-DISCLAIMER: Please do not include any Personally Identifiable Information within this survey such as physical addresses, phone numbers, merchant tokens, email addresses, account data, etc.
-Thank you,
-Your Multi-Channel Fulfillment Team
-This survey is hosted by an external party Qualtrics.com, so the link above does not lead to our website. Your responses are subject to Amazon's Privacy Notice. If you have any concerns about the authenticity of this e-mail or to find out more about Amazon's survey program, please vi</t>
-        </is>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" s="2" t="inlineStr">
+    <row r="30">
+      <c r="A30" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B37" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C37" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D37" s="2" t="inlineStr">
+      <c r="B30" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C30" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D30" s="2" t="inlineStr">
+        <is>
+          <t>Thu, 9 Apr 2026 14:28:35 +0000</t>
+        </is>
+      </c>
+      <c r="E30" s="2" t="inlineStr">
+        <is>
+          <t>Amazon Payments UK Limited &lt;seller-notification@amazon.com&gt;</t>
+        </is>
+      </c>
+      <c r="F30" s="2" t="inlineStr">
+        <is>
+          <t>Balance Paid on Your Selling on Amazon payment account</t>
+        </is>
+      </c>
+      <c r="G30" s="2" t="inlineStr"/>
+      <c r="H30" s="2" t="inlineStr">
+        <is>
+          <t>Dear Seller,
+ We have charged your (Visa) credit card for 62.05 in an attempt to settle your account balance.
+ Please note that the amount charged to your credit card may be less than the total amount you owe due to a credit limit imposed by your bank. In this case, we may continue to attempt charging your card until the remaining balance in your Amazon Selling on Amazon payment account is paid in full.
+ You can also use the Make a Payment feature to repay the balance you owe. For details, refer “Making a Payment” in Seller Central Help.
+ To view your payment activity anytime, please log in to your account and refer the Payments Report page.
+ Thank you for selling on Amazon.
+ Amazon Payments UK Limited
+Amazon Payments UK Limited, a private company limited by shares, is a company registered in England and Wales (registration number 11049457; VAT number: GB295 7604 60) with its registered office at 1 Principal Place, Worship St, London, EC2A 2FA, United Kingdom. Amazon Payments UK Limited is authorised by the UK Financial Conduct Authority under the Payment Services Regulations 2017 (reference number 799814) for the provision of payment services.
+ Was this e-mail helpful?
+ SPC-EUAmaz</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="2" t="inlineStr">
+        <is>
+          <t>付款/资金类</t>
+        </is>
+      </c>
+      <c r="B31" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C31" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D31" s="2" t="inlineStr">
         <is>
           <t>Tue, 7 Apr 2026 15:16:38 +0000</t>
         </is>
       </c>
-      <c r="E37" s="2" t="inlineStr">
+      <c r="E31" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;seller-notification@amazon.pl&gt;</t>
         </is>
       </c>
-      <c r="F37" s="2" t="inlineStr">
+      <c r="F31" s="2" t="inlineStr">
         <is>
           <t>Nieuregulowane saldo na koncie Amazon</t>
         </is>
       </c>
-      <c r="G37" s="2" t="inlineStr"/>
-      <c r="H37" s="2" t="inlineStr">
+      <c r="G31" s="2" t="inlineStr"/>
+      <c r="H31" s="2" t="inlineStr">
         <is>
           <t>Witamy!
  Masz na swoim koncie nieuregulowane saldo w wysokośc PLN 45.29. Obciążymy tą kwotą kartę kredytową zarejestrowaną jako metoda płatności dla Twojego konta
@@ -2320,40 +2024,40 @@
         </is>
       </c>
     </row>
-    <row r="38">
-      <c r="A38" s="2" t="inlineStr">
+    <row r="32">
+      <c r="A32" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B38" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C38" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D38" s="2" t="inlineStr">
+      <c r="B32" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C32" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D32" s="2" t="inlineStr">
         <is>
           <t>Mon, 6 Apr 2026 16:54:29 +0000</t>
         </is>
       </c>
-      <c r="E38" s="2" t="inlineStr">
+      <c r="E32" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F38" s="2" t="inlineStr">
+      <c r="F32" s="2" t="inlineStr">
         <is>
           <t>Refunds for digital services fees related to the Canadian DST will
  begin on April 15</t>
         </is>
       </c>
-      <c r="G38" s="2" t="inlineStr"/>
-      <c r="H38" s="2" t="inlineStr">
+      <c r="G32" s="2" t="inlineStr"/>
+      <c r="H32" s="2" t="inlineStr">
         <is>
           <t>96
  We’ll refund digital services fees and the taxes on those fees related to the Canadian digital services tax that we had charged from September 1, 2024, through August 15, 2025.
@@ -2370,39 +2074,39 @@
         </is>
       </c>
     </row>
-    <row r="39">
-      <c r="A39" s="2" t="inlineStr">
+    <row r="33">
+      <c r="A33" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B39" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C39" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D39" s="2" t="inlineStr">
+      <c r="B33" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C33" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D33" s="2" t="inlineStr">
         <is>
           <t>Sun, 5 Apr 2026 13:38:25 +0000</t>
         </is>
       </c>
-      <c r="E39" s="2" t="inlineStr">
+      <c r="E33" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F39" s="2" t="inlineStr">
+      <c r="F33" s="2" t="inlineStr">
         <is>
           <t>Your payment is on the way</t>
         </is>
       </c>
-      <c r="G39" s="2" t="inlineStr"/>
-      <c r="H39" s="2" t="inlineStr">
+      <c r="G33" s="2" t="inlineStr"/>
+      <c r="H33" s="2" t="inlineStr">
         <is>
           <t>96
 This title will display on mobile devices
@@ -2422,39 +2126,39 @@
         </is>
       </c>
     </row>
-    <row r="40">
-      <c r="A40" s="2" t="inlineStr">
+    <row r="34">
+      <c r="A34" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B40" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C40" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D40" s="2" t="inlineStr">
+      <c r="B34" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C34" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D34" s="2" t="inlineStr">
         <is>
           <t>Thu, 2 Apr 2026 15:38:29 +0000</t>
         </is>
       </c>
-      <c r="E40" s="2" t="inlineStr">
+      <c r="E34" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F40" s="2" t="inlineStr">
+      <c r="F34" s="2" t="inlineStr">
         <is>
           <t>Tu pago está en camino</t>
         </is>
       </c>
-      <c r="G40" s="2" t="inlineStr"/>
-      <c r="H40" s="2" t="inlineStr">
+      <c r="G34" s="2" t="inlineStr"/>
+      <c r="H34" s="2" t="inlineStr">
         <is>
           <t>96
 This title will display on mobile devices
@@ -2471,39 +2175,39 @@
         </is>
       </c>
     </row>
-    <row r="41">
-      <c r="A41" s="2" t="inlineStr">
+    <row r="35">
+      <c r="A35" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B41" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C41" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D41" s="2" t="inlineStr">
+      <c r="B35" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C35" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D35" s="2" t="inlineStr">
         <is>
           <t>Tue, 31 Mar 2026 12:51:47 +0000</t>
         </is>
       </c>
-      <c r="E41" s="2" t="inlineStr">
+      <c r="E35" s="2" t="inlineStr">
         <is>
           <t>Amazon Europe &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F41" s="2" t="inlineStr">
+      <c r="F35" s="2" t="inlineStr">
         <is>
           <t>Eco-contribution and EPR Pay on Behalf service fee charges</t>
         </is>
       </c>
-      <c r="G41" s="2" t="inlineStr"/>
-      <c r="H41" s="2" t="inlineStr">
+      <c r="G35" s="2" t="inlineStr"/>
+      <c r="H35" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">Amazon Services
  96
@@ -2526,39 +2230,39 @@
         </is>
       </c>
     </row>
-    <row r="42">
-      <c r="A42" s="2" t="inlineStr">
+    <row r="36">
+      <c r="A36" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B42" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C42" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D42" s="2" t="inlineStr">
+      <c r="B36" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C36" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D36" s="2" t="inlineStr">
         <is>
           <t>Mon, 30 Mar 2026 15:13:23 +0000</t>
         </is>
       </c>
-      <c r="E42" s="2" t="inlineStr">
+      <c r="E36" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F42" s="2" t="inlineStr">
+      <c r="F36" s="2" t="inlineStr">
         <is>
           <t>Your payment is on the way</t>
         </is>
       </c>
-      <c r="G42" s="2" t="inlineStr"/>
-      <c r="H42" s="2" t="inlineStr">
+      <c r="G36" s="2" t="inlineStr"/>
+      <c r="H36" s="2" t="inlineStr">
         <is>
           <t>96
 This title will display on mobile devices
@@ -2578,39 +2282,39 @@
         </is>
       </c>
     </row>
-    <row r="43">
-      <c r="A43" s="2" t="inlineStr">
+    <row r="37">
+      <c r="A37" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B43" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C43" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D43" s="2" t="inlineStr">
+      <c r="B37" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C37" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D37" s="2" t="inlineStr">
         <is>
           <t>Thu, 26 Mar 2026 17:33:22 +0000</t>
         </is>
       </c>
-      <c r="E43" s="2" t="inlineStr">
+      <c r="E37" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F43" s="2" t="inlineStr">
+      <c r="F37" s="2" t="inlineStr">
         <is>
           <t>View your China tax report for October - December 2025</t>
         </is>
       </c>
-      <c r="G43" s="2" t="inlineStr"/>
-      <c r="H43" s="2" t="inlineStr">
+      <c r="G37" s="2" t="inlineStr"/>
+      <c r="H37" s="2" t="inlineStr">
         <is>
           <t>96
  We’ve submitted your quarterly tax report to the Chinese tax authority. You can now download the report for reference.
@@ -2627,39 +2331,39 @@
         </is>
       </c>
     </row>
-    <row r="44">
-      <c r="A44" s="2" t="inlineStr">
+    <row r="38">
+      <c r="A38" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B44" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C44" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D44" s="2" t="inlineStr">
+      <c r="B38" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C38" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D38" s="2" t="inlineStr">
         <is>
           <t>Thu, 19 Mar 2026 15:38:31 +0000</t>
         </is>
       </c>
-      <c r="E44" s="2" t="inlineStr">
+      <c r="E38" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F44" s="2" t="inlineStr">
+      <c r="F38" s="2" t="inlineStr">
         <is>
           <t>Tu pago está en camino</t>
         </is>
       </c>
-      <c r="G44" s="2" t="inlineStr"/>
-      <c r="H44" s="2" t="inlineStr">
+      <c r="G38" s="2" t="inlineStr"/>
+      <c r="H38" s="2" t="inlineStr">
         <is>
           <t>96
 This title will display on mobile devices
@@ -2676,39 +2380,91 @@
         </is>
       </c>
     </row>
-    <row r="45">
-      <c r="A45" s="2" t="inlineStr">
+    <row r="39">
+      <c r="A39" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B45" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C45" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D45" s="2" t="inlineStr">
+      <c r="B39" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C39" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D39" s="2" t="inlineStr">
+        <is>
+          <t>Thu, 9 Apr 2026 12:03:53 +0000</t>
+        </is>
+      </c>
+      <c r="E39" s="2" t="inlineStr">
+        <is>
+          <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
+        </is>
+      </c>
+      <c r="F39" s="2" t="inlineStr">
+        <is>
+          <t>Reactivate your EU listings - GPSR compliance required</t>
+        </is>
+      </c>
+      <c r="G39" s="2" t="inlineStr"/>
+      <c r="H39" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">96
+ Reactivate your EU listings - GPSR compliance required
+ Hello Weihai EU,
+ Some of your listings have been deactivated from our European Union (EU) stores due to missing compliance information. This action does not impact your account health.
+ You can find examples of your deactivated listings at the bottom of this email, and the full list on your Account Health page. Review the affected listings and next steps to meet General Product Safety Regulation (GPSR) requirements below.
+ Submit compliance information
+ Submit compliance information
+ How do I reactivate my listings?
+ To reactivate your listings, provide the required GPSR compliance information by following the instructions below:
+-
+ Go to your Account Health page .
+- Select 'Add filters' and check 'Listing removed' in the "Filter by action taken" column.
+- Click 'Submit' next to the deactivated listing and follow the instructions provided.
+- Follow the steps on Suppressed listings to resolve any outstanding listing issues. Existing issues prevent listings from being reactivated, even if you’ve fulfilled all compliance requirements.
+ Note: If you’ve recently submitted information on your Account Health page, and no longer </t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="2" t="inlineStr">
+        <is>
+          <t>产品链接/合规类</t>
+        </is>
+      </c>
+      <c r="B40" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C40" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D40" s="2" t="inlineStr">
         <is>
           <t>Wed, 8 Apr 2026 10:50:30 +0000</t>
         </is>
       </c>
-      <c r="E45" s="2" t="inlineStr">
+      <c r="E40" s="2" t="inlineStr">
         <is>
           <t>Amazon Europe &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F45" s="2" t="inlineStr">
+      <c r="F40" s="2" t="inlineStr">
         <is>
           <t>EU and UK Compliance Brief</t>
         </is>
       </c>
-      <c r="G45" s="2" t="inlineStr"/>
-      <c r="H45" s="2" t="inlineStr">
+      <c r="G40" s="2" t="inlineStr"/>
+      <c r="H40" s="2" t="inlineStr">
         <is>
           <t>Amazon Europe
  96
@@ -2729,39 +2485,39 @@
         </is>
       </c>
     </row>
-    <row r="46">
-      <c r="A46" s="2" t="inlineStr">
+    <row r="41">
+      <c r="A41" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B46" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C46" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D46" s="2" t="inlineStr">
+      <c r="B41" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C41" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D41" s="2" t="inlineStr">
         <is>
           <t>Wed, 8 Apr 2026 10:38:53 +0000</t>
         </is>
       </c>
-      <c r="E46" s="2" t="inlineStr">
+      <c r="E41" s="2" t="inlineStr">
         <is>
           <t>Amazon Europe &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F46" s="2" t="inlineStr">
+      <c r="F41" s="2" t="inlineStr">
         <is>
           <t>EU and UK Compliance Brief</t>
         </is>
       </c>
-      <c r="G46" s="2" t="inlineStr"/>
-      <c r="H46" s="2" t="inlineStr">
+      <c r="G41" s="2" t="inlineStr"/>
+      <c r="H41" s="2" t="inlineStr">
         <is>
           <t>Amazon Europe
  96
@@ -2782,40 +2538,40 @@
         </is>
       </c>
     </row>
-    <row r="47">
-      <c r="A47" s="2" t="inlineStr">
+    <row r="42">
+      <c r="A42" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B47" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C47" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D47" s="2" t="inlineStr">
+      <c r="B42" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C42" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D42" s="2" t="inlineStr">
         <is>
           <t>Wed, 8 Apr 2026 10:23:33 +0000</t>
         </is>
       </c>
-      <c r="E47" s="2" t="inlineStr">
+      <c r="E42" s="2" t="inlineStr">
         <is>
           <t>The Amazon Europe team &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F47" s="2" t="inlineStr">
+      <c r="F42" s="2" t="inlineStr">
         <is>
           <t>VAT Calculation Services will calculate VAT by shipment as of June
  1</t>
         </is>
       </c>
-      <c r="G47" s="2" t="inlineStr"/>
-      <c r="H47" s="2" t="inlineStr">
+      <c r="G42" s="2" t="inlineStr"/>
+      <c r="H42" s="2" t="inlineStr">
         <is>
           <t>96
  New tax calculation method ensures compliance with European e-invoicing mandates.
@@ -2831,39 +2587,39 @@
         </is>
       </c>
     </row>
-    <row r="48">
-      <c r="A48" s="2" t="inlineStr">
+    <row r="43">
+      <c r="A43" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B48" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C48" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D48" s="2" t="inlineStr">
+      <c r="B43" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C43" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D43" s="2" t="inlineStr">
         <is>
           <t>Thu, 2 Apr 2026 04:56:03 +0000</t>
         </is>
       </c>
-      <c r="E48" s="2" t="inlineStr">
+      <c r="E43" s="2" t="inlineStr">
         <is>
           <t>"ppwr-cn-seller-compliance@amazon.com" &lt;ppwr-cn-seller-compliance@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F48" s="2" t="inlineStr">
+      <c r="F43" s="2" t="inlineStr">
         <is>
           <t>RE:[CASE 12309992722] 需要采取行动：请向亚马逊提交您的EPR包装法注册号</t>
         </is>
       </c>
-      <c r="G48" s="2" t="inlineStr"/>
-      <c r="H48" s="2" t="inlineStr">
+      <c r="G43" s="2" t="inlineStr"/>
+      <c r="H43" s="2" t="inlineStr">
         <is>
           <t>【请勿回复】
 尊敬的销售合作伙伴，
@@ -2886,39 +2642,39 @@
         </is>
       </c>
     </row>
-    <row r="49">
-      <c r="A49" s="2" t="inlineStr">
+    <row r="44">
+      <c r="A44" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B49" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C49" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D49" s="2" t="inlineStr">
+      <c r="B44" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C44" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D44" s="2" t="inlineStr">
         <is>
           <t>Thu, 2 Apr 2026 02:19:17 +0000</t>
         </is>
       </c>
-      <c r="E49" s="2" t="inlineStr">
+      <c r="E44" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F49" s="2" t="inlineStr">
+      <c r="F44" s="2" t="inlineStr">
         <is>
           <t>Submit product safety documentation to reactivate listings</t>
         </is>
       </c>
-      <c r="G49" s="2" t="inlineStr"/>
-      <c r="H49" s="2" t="inlineStr">
+      <c r="G44" s="2" t="inlineStr"/>
+      <c r="H44" s="2" t="inlineStr">
         <is>
           <t>96
  Submit product safety documentation to reactivate listings
@@ -2936,39 +2692,39 @@
         </is>
       </c>
     </row>
-    <row r="50">
-      <c r="A50" s="2" t="inlineStr">
+    <row r="45">
+      <c r="A45" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B50" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C50" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D50" s="2" t="inlineStr">
+      <c r="B45" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C45" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D45" s="2" t="inlineStr">
         <is>
           <t>Thu, 2 Apr 2026 02:18:50 +0000</t>
         </is>
       </c>
-      <c r="E50" s="2" t="inlineStr">
+      <c r="E45" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F50" s="2" t="inlineStr">
+      <c r="F45" s="2" t="inlineStr">
         <is>
           <t>Submit product safety documentation to reactivate listings</t>
         </is>
       </c>
-      <c r="G50" s="2" t="inlineStr"/>
-      <c r="H50" s="2" t="inlineStr">
+      <c r="G45" s="2" t="inlineStr"/>
+      <c r="H45" s="2" t="inlineStr">
         <is>
           <t>96
  Submit product safety documentation to reactivate listings
@@ -2986,39 +2742,39 @@
         </is>
       </c>
     </row>
-    <row r="51">
-      <c r="A51" s="2" t="inlineStr">
+    <row r="46">
+      <c r="A46" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B51" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C51" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D51" s="2" t="inlineStr">
+      <c r="B46" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C46" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D46" s="2" t="inlineStr">
         <is>
           <t>Tue, 31 Mar 2026 21:25:34 +0000</t>
         </is>
       </c>
-      <c r="E51" s="2" t="inlineStr">
+      <c r="E46" s="2" t="inlineStr">
         <is>
           <t>"Amazon Seller Central notifications (Do not reply)" &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F51" s="2" t="inlineStr">
+      <c r="F46" s="2" t="inlineStr">
         <is>
           <t>Address compliance requirements for your listings</t>
         </is>
       </c>
-      <c r="G51" s="2" t="inlineStr"/>
-      <c r="H51" s="2" t="inlineStr">
+      <c r="G46" s="2" t="inlineStr"/>
+      <c r="H46" s="2" t="inlineStr">
         <is>
           <t>96
 Action required: Important information about your product listings
@@ -3038,39 +2794,39 @@
         </is>
       </c>
     </row>
-    <row r="52">
-      <c r="A52" s="2" t="inlineStr">
+    <row r="47">
+      <c r="A47" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B52" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C52" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D52" s="2" t="inlineStr">
+      <c r="B47" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C47" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D47" s="2" t="inlineStr">
         <is>
           <t>Mon, 30 Mar 2026 07:07:52 +0000</t>
         </is>
       </c>
-      <c r="E52" s="2" t="inlineStr">
+      <c r="E47" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F52" s="2" t="inlineStr">
+      <c r="F47" s="2" t="inlineStr">
         <is>
           <t>Submit product safety documentation to reactivate listings</t>
         </is>
       </c>
-      <c r="G52" s="2" t="inlineStr"/>
-      <c r="H52" s="2" t="inlineStr">
+      <c r="G47" s="2" t="inlineStr"/>
+      <c r="H47" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">96
  Submit product safety documentation to reactivate listings
@@ -3088,39 +2844,39 @@
         </is>
       </c>
     </row>
-    <row r="53">
-      <c r="A53" s="2" t="inlineStr">
+    <row r="48">
+      <c r="A48" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B53" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C53" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D53" s="2" t="inlineStr">
+      <c r="B48" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C48" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D48" s="2" t="inlineStr">
         <is>
           <t>Sat, 28 Mar 2026 13:21:45 +0000</t>
         </is>
       </c>
-      <c r="E53" s="2" t="inlineStr">
+      <c r="E48" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F53" s="2" t="inlineStr">
+      <c r="F48" s="2" t="inlineStr">
         <is>
           <t>Submit product safety documentation to reactivate listings</t>
         </is>
       </c>
-      <c r="G53" s="2" t="inlineStr"/>
-      <c r="H53" s="2" t="inlineStr">
+      <c r="G48" s="2" t="inlineStr"/>
+      <c r="H48" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">96
  Submit product safety documentation to reactivate listings
@@ -3138,39 +2894,39 @@
         </is>
       </c>
     </row>
-    <row r="54">
-      <c r="A54" s="2" t="inlineStr">
+    <row r="49">
+      <c r="A49" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B54" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C54" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D54" s="2" t="inlineStr">
+      <c r="B49" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C49" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D49" s="2" t="inlineStr">
         <is>
           <t>Sat, 28 Mar 2026 13:01:16 +0000</t>
         </is>
       </c>
-      <c r="E54" s="2" t="inlineStr">
+      <c r="E49" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F54" s="2" t="inlineStr">
+      <c r="F49" s="2" t="inlineStr">
         <is>
           <t>Submit product safety documentation to reactivate listings</t>
         </is>
       </c>
-      <c r="G54" s="2" t="inlineStr"/>
-      <c r="H54" s="2" t="inlineStr">
+      <c r="G49" s="2" t="inlineStr"/>
+      <c r="H49" s="2" t="inlineStr">
         <is>
           <t>96
  Submit product safety documentation to reactivate listings
@@ -3188,39 +2944,39 @@
         </is>
       </c>
     </row>
-    <row r="55">
-      <c r="A55" s="2" t="inlineStr">
+    <row r="50">
+      <c r="A50" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B55" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C55" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D55" s="2" t="inlineStr">
+      <c r="B50" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C50" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D50" s="2" t="inlineStr">
         <is>
           <t>Fri, 27 Mar 2026 14:37:14 +0000</t>
         </is>
       </c>
-      <c r="E55" s="2" t="inlineStr">
+      <c r="E50" s="2" t="inlineStr">
         <is>
           <t>Sell with Amazon &lt;no-reply@sell.amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F55" s="2" t="inlineStr">
+      <c r="F50" s="2" t="inlineStr">
         <is>
           <t>Live Q&amp;A on customer feedback with experienced sellers</t>
         </is>
       </c>
-      <c r="G55" s="2" t="inlineStr"/>
-      <c r="H55" s="2" t="inlineStr">
+      <c r="G50" s="2" t="inlineStr"/>
+      <c r="H50" s="2" t="inlineStr">
         <is>
           <t>[Amazon logo](https://go.amazonsellerservices.com/e/229492/-ref--spc-em-na-frm-20260324/7z2bw3r/6577485148/h/BOm7kDreq_ieAJ8P9nkJWZ402nkYiTu_wgkPAn3aZYs)
 Connect with sellers experienced in customer feedback
@@ -3235,39 +2991,39 @@
         </is>
       </c>
     </row>
-    <row r="56">
-      <c r="A56" s="2" t="inlineStr">
+    <row r="51">
+      <c r="A51" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B56" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C56" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D56" s="2" t="inlineStr">
+      <c r="B51" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C51" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D51" s="2" t="inlineStr">
         <is>
           <t>Fri, 27 Mar 2026 13:18:53 +0000</t>
         </is>
       </c>
-      <c r="E56" s="2" t="inlineStr">
+      <c r="E51" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F56" s="2" t="inlineStr">
+      <c r="F51" s="2" t="inlineStr">
         <is>
           <t>Submit product safety documentation to reactivate listings</t>
         </is>
       </c>
-      <c r="G56" s="2" t="inlineStr"/>
-      <c r="H56" s="2" t="inlineStr">
+      <c r="G51" s="2" t="inlineStr"/>
+      <c r="H51" s="2" t="inlineStr">
         <is>
           <t>96
  Submit product safety documentation to reactivate listings
@@ -3285,39 +3041,39 @@
         </is>
       </c>
     </row>
-    <row r="57">
-      <c r="A57" s="2" t="inlineStr">
+    <row r="52">
+      <c r="A52" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B57" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C57" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D57" s="2" t="inlineStr">
+      <c r="B52" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C52" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D52" s="2" t="inlineStr">
         <is>
           <t>Fri, 27 Mar 2026 13:13:28 +0000</t>
         </is>
       </c>
-      <c r="E57" s="2" t="inlineStr">
+      <c r="E52" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F57" s="2" t="inlineStr">
+      <c r="F52" s="2" t="inlineStr">
         <is>
           <t>Submit product safety documentation to reactivate listings</t>
         </is>
       </c>
-      <c r="G57" s="2" t="inlineStr"/>
-      <c r="H57" s="2" t="inlineStr">
+      <c r="G52" s="2" t="inlineStr"/>
+      <c r="H52" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">96
  Submit product safety documentation to reactivate listings
@@ -3335,39 +3091,39 @@
         </is>
       </c>
     </row>
-    <row r="58">
-      <c r="A58" s="2" t="inlineStr">
+    <row r="53">
+      <c r="A53" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B58" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C58" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D58" s="2" t="inlineStr">
+      <c r="B53" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C53" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D53" s="2" t="inlineStr">
         <is>
           <t>Fri, 27 Mar 2026 12:51:52 +0000</t>
         </is>
       </c>
-      <c r="E58" s="2" t="inlineStr">
+      <c r="E53" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F58" s="2" t="inlineStr">
+      <c r="F53" s="2" t="inlineStr">
         <is>
           <t>Submit product safety documentation to reactivate listings</t>
         </is>
       </c>
-      <c r="G58" s="2" t="inlineStr"/>
-      <c r="H58" s="2" t="inlineStr">
+      <c r="G53" s="2" t="inlineStr"/>
+      <c r="H53" s="2" t="inlineStr">
         <is>
           <t>96
  Submit product safety documentation to reactivate listings
@@ -3385,39 +3141,39 @@
         </is>
       </c>
     </row>
-    <row r="59">
-      <c r="A59" s="2" t="inlineStr">
+    <row r="54">
+      <c r="A54" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B59" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C59" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D59" s="2" t="inlineStr">
+      <c r="B54" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C54" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D54" s="2" t="inlineStr">
         <is>
           <t>Fri, 27 Mar 2026 08:16:10 +0000</t>
         </is>
       </c>
-      <c r="E59" s="2" t="inlineStr">
+      <c r="E54" s="2" t="inlineStr">
         <is>
           <t>"fba-3p-buyability-improvement-us@amazon.com" &lt;fba-3p-buyability-improvement-us@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F59" s="2" t="inlineStr">
+      <c r="F54" s="2" t="inlineStr">
         <is>
           <t>Action Required: Website Suppressed ASINs</t>
         </is>
       </c>
-      <c r="G59" s="2" t="inlineStr"/>
-      <c r="H59" s="2" t="inlineStr">
+      <c r="G54" s="2" t="inlineStr"/>
+      <c r="H54" s="2" t="inlineStr">
         <is>
           <t>Dear Seller,
 We are part of Buyability Audit team at Amazon. The Buyability program aims to identify and eliminate root causes leading to Buyability drop-off. We are contacting you to let you know that you could be missing out on sales opportunities due to the suppression of some of your ASINs.
@@ -3432,39 +3188,39 @@
         </is>
       </c>
     </row>
-    <row r="60">
-      <c r="A60" s="2" t="inlineStr">
+    <row r="55">
+      <c r="A55" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B60" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C60" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D60" s="2" t="inlineStr">
+      <c r="B55" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C55" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D55" s="2" t="inlineStr">
         <is>
           <t>Thu, 26 Mar 2026 15:17:29 +0000</t>
         </is>
       </c>
-      <c r="E60" s="2" t="inlineStr">
+      <c r="E55" s="2" t="inlineStr">
         <is>
           <t>"fba-3p-buyability-improvement-us@amazon.com" &lt;fba-3p-buyability-improvement-us@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F60" s="2" t="inlineStr">
+      <c r="F55" s="2" t="inlineStr">
         <is>
           <t>Action Required: Website Suppressed ASINs</t>
         </is>
       </c>
-      <c r="G60" s="2" t="inlineStr"/>
-      <c r="H60" s="2" t="inlineStr">
+      <c r="G55" s="2" t="inlineStr"/>
+      <c r="H55" s="2" t="inlineStr">
         <is>
           <t>Dear Seller,
 We are part of Buyability Audit team at Amazon. The Buyability program aims to identify and eliminate root causes leading to Buyability drop-off. We are contacting you to let you know that you could be missing out on sales opportunities due to the suppression of some of your ASINs.
@@ -3479,39 +3235,39 @@
         </is>
       </c>
     </row>
-    <row r="61">
-      <c r="A61" s="2" t="inlineStr">
+    <row r="56">
+      <c r="A56" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B61" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C61" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D61" s="2" t="inlineStr">
+      <c r="B56" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C56" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D56" s="2" t="inlineStr">
         <is>
           <t>Tue, 24 Mar 2026 14:28:08 +0000</t>
         </is>
       </c>
-      <c r="E61" s="2" t="inlineStr">
+      <c r="E56" s="2" t="inlineStr">
         <is>
           <t>"fba-3p-buyability-improvement-us@amazon.com" &lt;fba-3p-buyability-improvement-us@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F61" s="2" t="inlineStr">
+      <c r="F56" s="2" t="inlineStr">
         <is>
           <t>Action Required: Website Suppressed ASINs</t>
         </is>
       </c>
-      <c r="G61" s="2" t="inlineStr"/>
-      <c r="H61" s="2" t="inlineStr">
+      <c r="G56" s="2" t="inlineStr"/>
+      <c r="H56" s="2" t="inlineStr">
         <is>
           <t>Dear Seller,
 We are part of Buyability Audit team at Amazon. The Buyability program aims to identify and eliminate root causes leading to Buyability drop-off. We are contacting you to let you know that you could be missing out on sales opportunities due to the suppression of some of your ASINs.
@@ -3526,39 +3282,39 @@
         </is>
       </c>
     </row>
-    <row r="62">
-      <c r="A62" s="2" t="inlineStr">
+    <row r="57">
+      <c r="A57" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B62" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C62" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D62" s="2" t="inlineStr">
+      <c r="B57" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C57" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D57" s="2" t="inlineStr">
         <is>
           <t>Tue, 24 Mar 2026 04:25:09 +0000</t>
         </is>
       </c>
-      <c r="E62" s="2" t="inlineStr">
+      <c r="E57" s="2" t="inlineStr">
         <is>
           <t>Fulfillment by Amazon Operations &lt;fba-noreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F62" s="2" t="inlineStr">
+      <c r="F57" s="2" t="inlineStr">
         <is>
           <t>Your Amazon.com Inventory - Action Required</t>
         </is>
       </c>
-      <c r="G62" s="2" t="inlineStr"/>
-      <c r="H62" s="2" t="inlineStr">
+      <c r="G57" s="2" t="inlineStr"/>
+      <c r="H57" s="2" t="inlineStr">
         <is>
           <t>Dear Weihai US,
 We have recently restricted listings for the product(s) listed below on Amazon.com.
@@ -3577,40 +3333,40 @@
         </is>
       </c>
     </row>
-    <row r="63">
-      <c r="A63" s="2" t="inlineStr">
+    <row r="58">
+      <c r="A58" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B63" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C63" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D63" s="2" t="inlineStr">
+      <c r="B58" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C58" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D58" s="2" t="inlineStr">
         <is>
           <t>Mon, 23 Mar 2026 11:52:08 +0000</t>
         </is>
       </c>
-      <c r="E63" s="2" t="inlineStr">
+      <c r="E58" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F63" s="2" t="inlineStr">
+      <c r="F58" s="2" t="inlineStr">
         <is>
           <t>Submit UK import details by 21/05/2026 to avoid shipping
  restrictions</t>
         </is>
       </c>
-      <c r="G63" s="2" t="inlineStr"/>
-      <c r="H63" s="2" t="inlineStr">
+      <c r="G58" s="2" t="inlineStr"/>
+      <c r="H58" s="2" t="inlineStr">
         <is>
           <t>96
  Submit UK import details by 21/05/2026 to avoid shipping restrictions
@@ -3629,39 +3385,39 @@
         </is>
       </c>
     </row>
-    <row r="64">
-      <c r="A64" s="2" t="inlineStr">
+    <row r="59">
+      <c r="A59" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B64" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C64" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D64" s="2" t="inlineStr">
+      <c r="B59" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C59" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D59" s="2" t="inlineStr">
         <is>
           <t>Mon, 23 Mar 2026 07:21:52 +0000</t>
         </is>
       </c>
-      <c r="E64" s="2" t="inlineStr">
+      <c r="E59" s="2" t="inlineStr">
         <is>
           <t>Amazon Europe &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F64" s="2" t="inlineStr">
+      <c r="F59" s="2" t="inlineStr">
         <is>
           <t>Add products to Amazon.nl for Pan EU eligibility</t>
         </is>
       </c>
-      <c r="G64" s="2" t="inlineStr"/>
-      <c r="H64" s="2" t="inlineStr">
+      <c r="G59" s="2" t="inlineStr"/>
+      <c r="H59" s="2" t="inlineStr">
         <is>
           <t>Add products to Amazon.nl for Pan EU eligibility 96
  Complete Pan EU enrollment: Add NL products now
@@ -3671,39 +3427,39 @@
         </is>
       </c>
     </row>
-    <row r="65">
-      <c r="A65" s="2" t="inlineStr">
+    <row r="60">
+      <c r="A60" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B65" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C65" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D65" s="2" t="inlineStr">
+      <c r="B60" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C60" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D60" s="2" t="inlineStr">
         <is>
           <t>Sat, 21 Mar 2026 21:58:00 +0000</t>
         </is>
       </c>
-      <c r="E65" s="2" t="inlineStr">
+      <c r="E60" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F65" s="2" t="inlineStr">
+      <c r="F60" s="2" t="inlineStr">
         <is>
           <t>Submit product safety documentation to reactivate listings</t>
         </is>
       </c>
-      <c r="G65" s="2" t="inlineStr"/>
-      <c r="H65" s="2" t="inlineStr">
+      <c r="G60" s="2" t="inlineStr"/>
+      <c r="H60" s="2" t="inlineStr">
         <is>
           <t>96
  Submit product safety documentation to reactivate listings
@@ -3721,39 +3477,39 @@
         </is>
       </c>
     </row>
-    <row r="66">
-      <c r="A66" s="2" t="inlineStr">
+    <row r="61">
+      <c r="A61" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B66" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C66" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D66" s="2" t="inlineStr">
+      <c r="B61" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C61" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D61" s="2" t="inlineStr">
         <is>
           <t>Fri, 20 Mar 2026 21:10:27 +0000</t>
         </is>
       </c>
-      <c r="E66" s="2" t="inlineStr">
+      <c r="E61" s="2" t="inlineStr">
         <is>
           <t>"fba-3p-buyability-improvement-ca@amazon.com" &lt;fba-3p-buyability-improvement-ca@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F66" s="2" t="inlineStr">
+      <c r="F61" s="2" t="inlineStr">
         <is>
           <t>Action Required: Website Suppressed ASINs</t>
         </is>
       </c>
-      <c r="G66" s="2" t="inlineStr"/>
-      <c r="H66" s="2" t="inlineStr">
+      <c r="G61" s="2" t="inlineStr"/>
+      <c r="H61" s="2" t="inlineStr">
         <is>
           <t>Dear Seller,
 We are contacting you to let you know that you could be missing out on sales opportunities because of your incomplete listings.
@@ -3766,6 +3522,247 @@
  https://sellercentral.amazon.ca/performance/account/health/compliance-request
 If you need further help, please raise a case via contact us. - https://sellercentral.amazon.ca/cu/contact-us?ref=xx_ContactUs_xxxx_helphub
 If you are not the correct point of contact, please re-direct this email to the correct point of contact</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="2" t="inlineStr">
+        <is>
+          <t>法务/侵权类</t>
+        </is>
+      </c>
+      <c r="B62" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C62" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D62" s="2" t="inlineStr">
+        <is>
+          <t>Thu, 9 Apr 2026 17:17:52 +0000</t>
+        </is>
+      </c>
+      <c r="E62" s="2" t="inlineStr">
+        <is>
+          <t>The Amazon Services team &lt;donotreply@amazon.com&gt;</t>
+        </is>
+      </c>
+      <c r="F62" s="2" t="inlineStr">
+        <is>
+          <t>Introducing Global Warehousing &amp; Distribution</t>
+        </is>
+      </c>
+      <c r="G62" s="2" t="inlineStr"/>
+      <c r="H62" s="2" t="inlineStr">
+        <is>
+          <t>96
+ Store inventory at origin in China with lower costs and faster speeds.
+ Hello,
+ Starting April 9, 2026, you can store your inventory in bulk at a lower cost in our new Global Warehousing &amp; Distribution (GWD) facility in Shenzhen, China, and seamlessly replenish to our US fulfillment network when needed.
+ By using GWD in Shenzhen, you can:
+- Reduce storage costs by up to 45% compared to US Amazon Warehousing and Distribution (AWD).
+- Get inventory to US fulfillment centers up to seven days faster when paired with Amazon Global Logistics (AGL).
+- Maintain consistently healthy inventory levels through reliable, automated cross-border replenishment.
+- Choose your management style of either AI-powered automated replenishment or manual control while we handle the entire cross-border logistics process.
+- Streamline your supply chain of shipping, customs clearance, and delivery to our fulfillment centers all through a single, integrated solution. GWD is the first step in our Next Generation of Global Selling vision — where you list once, bring your inventory to the warehouse at origin, and sell it globally from day one. This vision transforms cross-border commerce: you focus on buildin</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="2" t="inlineStr">
+        <is>
+          <t>法务/侵权类</t>
+        </is>
+      </c>
+      <c r="B63" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C63" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D63" s="2" t="inlineStr">
+        <is>
+          <t>Thu, 9 Apr 2026 16:27:24 +0000</t>
+        </is>
+      </c>
+      <c r="E63" s="2" t="inlineStr">
+        <is>
+          <t>donotreply@amazon.com</t>
+        </is>
+      </c>
+      <c r="F63" s="2" t="inlineStr">
+        <is>
+          <t>Your Amazon.ca Fulfillment by Amazon Merchant Invoice for 3/2026 (Votre Facture Expédié Par Amazon Amazon.ca pour le mois de 3/2026)</t>
+        </is>
+      </c>
+      <c r="G63" s="2" t="inlineStr"/>
+      <c r="H63" s="2" t="inlineStr">
+        <is>
+          <t>Dear Shen zhen shi wei hai zhong xin ke ji you xian,
+We are writing to inform you that your electronic Fulfillment by Amazon Merchant Invoice for the month of 3/2026 is now available in your Seller Central Account.
+To access your invoice, go to your Seller Central Account &gt; Reports &gt; Tax Document Library &gt; Seller Fee Tax Invoices.
+In your Seller Central account, you will be able to view, download or print your invoice.
+If you have any questions, please contact Seller Support.
+Best regards,
+Amazon.ca
+ Monsieur/Madame Shen zhen shi wei hai zhong xin ke ji you xian,
+Nous vous écrivons pour vous informer que votre Facture Expédié Par Amazon pour le mois de 3/2026 est maintenant disponible dans votre compte Seller Central.
+Pour accéder à votre facture, rendez-vous sur votre compte Seller Central et veuillez accéder à la page Rapports &gt; Bibliothèque d'informations fiscales &gt; Factures des frais du vendeur.
+Dans votre compte Seller Central, vous pourrez afficher, télécharger ou imprimer votre facture.
+Pour toute question, contactez le Support Vendeur.
+Cordialement,
+Amazon.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="2" t="inlineStr">
+        <is>
+          <t>法务/侵权类</t>
+        </is>
+      </c>
+      <c r="B64" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C64" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D64" s="2" t="inlineStr">
+        <is>
+          <t>Thu, 9 Apr 2026 11:49:51 +0000</t>
+        </is>
+      </c>
+      <c r="E64" s="2" t="inlineStr">
+        <is>
+          <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
+        </is>
+      </c>
+      <c r="F64" s="2" t="inlineStr">
+        <is>
+          <t>Riattivare le offerte nell'UE - Richiesta la conformità al Regolamento sulla sicurezza generale dei prodotti</t>
+        </is>
+      </c>
+      <c r="G64" s="2" t="inlineStr"/>
+      <c r="H64" s="2" t="inlineStr">
+        <is>
+          <t>96
+ Riattivare le offerte nell'UE - Richiesta la conformità al Regolamento sulla sicurezza generale dei prodotti
+ Gentile Weihai EU,
+ Alcune delle tue offerte sono state disattivate nei nostri negozi dell'Unione europea a causa della mancanza di informazioni relative alla conformità. Questa azione non avrà alcun impatto sullo stato del tuo account.
+ Puoi trovare esempi delle tue offerte disattivate in fondo a questa e-mail e l'elenco completo nella pagina Stato dell'account. Rivedi le offerte interessate e i passaggi successivi per soddisfare i requisiti del Regolamento sulla sicurezza generale dei prodotti riportati di seguito.
+ Inviare le informazioni sulla conformità
+ Inviare le informazioni sulla conformità
+ Come faccio a riattivare le mie offerte?
+ Per riattivare le offerte, fornisci le informazioni richieste relative alla conformità al regolamento sulla sicurezza generale dei prodotti seguendo le istruzioni riportate di seguito:
+-
+ Vai alla pagina Stato dell'account .
+- Seleziona "Aggiungi filtri" e quindi "Offerta rimossa" nella colonna "Filtra per azione intrapresa".
+- Clicca su "Invia" accanto all'offerta disattivata e segui le istruzioni fornite.
+- Segui la procedura indi</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="2" t="inlineStr">
+        <is>
+          <t>法务/侵权类</t>
+        </is>
+      </c>
+      <c r="B65" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C65" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D65" s="2" t="inlineStr">
+        <is>
+          <t>Thu, 9 Apr 2026 10:53:45 +0000</t>
+        </is>
+      </c>
+      <c r="E65" s="2" t="inlineStr">
+        <is>
+          <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
+        </is>
+      </c>
+      <c r="F65" s="2" t="inlineStr">
+        <is>
+          <t>Las tarifas por puesta de inventario a disposición de Amazon y retirada de Logística de Amazon se cobrarán a medida que se procesen las unidades</t>
+        </is>
+      </c>
+      <c r="G65" s="2" t="inlineStr"/>
+      <c r="H65" s="2" t="inlineStr">
+        <is>
+          <t>96
+ Las tarifas por retirada y puesta de inventario a disposición de Amazon de Logística de Amazon se cobrarán ahora por unidad en el momento en que cada unidad se retire o se ponga a nuestra disposición.
+ Hola:
+ Con entrada en vigor el 1 de mayo de 2026, las tarifas por puesta de inventario a disposición de Amazon y retirada de Logística de Amazon se cobrarán por unidad en el momento en que cada unidad se retire o se ponga a nuestra disposición. Con esta actualización, seguimos los estándares del sector y te proporcionamos más visibilidad sobre tus actividades de retirada y puesta de inventario a nuestra disposición.
+ Este cambio sólo afecta al momento en que se te cobra. No hay cambios en las tarifas por retirada y puesta de inventario a disposición de Amazon. Antes, estas tarifas se cobraban una vez que se completaba toda la solicitud de retirada o puesta de inventario a disposición de Amazon.
+ No es necesario que hagas nada. Este cambio se aplicará automáticamente a las nuevas solicitudes de retirada y puesta de inventario a disposición de Amazon creadas a partir del 1 de mayo.
+ Para consultar los cargos por envío de las retiradas y puestas de inventario a nuestra disposición y</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="2" t="inlineStr">
+        <is>
+          <t>法务/侵权类</t>
+        </is>
+      </c>
+      <c r="B66" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C66" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D66" s="2" t="inlineStr">
+        <is>
+          <t>Thu, 9 Apr 2026 09:19:33 +0000</t>
+        </is>
+      </c>
+      <c r="E66" s="2" t="inlineStr">
+        <is>
+          <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
+        </is>
+      </c>
+      <c r="F66" s="2" t="inlineStr">
+        <is>
+          <t>Opłaty za usunięcie i likwidację zapasów FBA naliczane podczas przetwarzania jednostek</t>
+        </is>
+      </c>
+      <c r="G66" s="2" t="inlineStr"/>
+      <c r="H66" s="2" t="inlineStr">
+        <is>
+          <t>96
+ Opłaty za wycofanie i usunięcie zapasów w ramach FBA będą teraz pobierane od każdej jednostki w momencie jej wycofania lub usunięcia.
+ Dzień dobry,
+ od 1 maja 2026 r. opłaty za wycofanie i usunięcie w ramach usługi Realizacja przez Amazon (FBA) będą pobierane od każdej jednostki w momencie jej wycofania lub usunięcia. Aktualizacja jest zgodna ze standardami branżowymi i zapewnia większą przejrzystość działań związanych z wycofywaniem i usuwaniem zapasów.
+ Zmiana dotyczy wyłącznie momentu pobrania opłaty. Stawki opłat za wycofanie i usunięcie zapasów pozostają bez zmian. Wcześniej opłaty były pobierane po zakończeniu realizacji całego zlecenia wycofania zapasów lub zlecenia usunięcia zapasów.
+ Nie musisz podejmować żadnych działań. Zmiana zostanie automatycznie zastosowana do nowych zleceń wycofania zapasów i zleceń usunięcia zapasów utworzonych od 1 maja.
+ Aby sprawdzić opłaty na poziomie przesyłki dotyczące wycofania i usunięcia zapasów oraz terminy wycofywania jednostek, przejdź na kartę Transakcje .
+ Więcej informacji znajdziesz na stronie Aktualizacje opłat za wycofanie i usunięcie zapasów w ramach FBA .
+ Zespół Amazon Europe
+ Zgłoś problem z tym e-mailem
+ Jeśli masz pytani</t>
         </is>
       </c>
     </row>
@@ -6375,7 +6372,7 @@
     <row r="121">
       <c r="A121" s="2" t="inlineStr">
         <is>
-          <t>法务/侵权类</t>
+          <t>货件/库存类</t>
         </is>
       </c>
       <c r="B121" s="2" t="inlineStr">
@@ -6390,77 +6387,21 @@
       </c>
       <c r="D121" s="2" t="inlineStr">
         <is>
-          <t>Tue, 17 Mar 2026 05:46:24 +0000</t>
+          <t>Mon, 6 Apr 2026 22:48:38 +0000</t>
         </is>
       </c>
       <c r="E121" s="2" t="inlineStr">
         <is>
-          <t>Notificações do Seller Central da Amazon (não responder) &lt;donotreply@amazon.com&gt;</t>
+          <t>Fulfilment by Amazon &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
       <c r="F121" s="2" t="inlineStr">
         <is>
-          <t>A Amazon enviou os itens vendidos</t>
+          <t>Remove aged, stranded and unfulfillable inventory by April 30</t>
         </is>
       </c>
       <c r="G121" s="2" t="inlineStr"/>
       <c r="H121" s="2" t="inlineStr">
-        <is>
-          <t>96
- Processamos e enviamos seus pedidos do programa FBA - Logística da Amazon.
- Olá,
- Processamos e enviamos seus pedidos do programa FBA - Logística da Amazon para clientes. Veja os detalhes abaixo para até 20 dos pedidos mais recentes.
- Para acompanhar o status desses pedidos e de todos os seus pedidos, acesse a página Gerenciar pedidos no Seller Central.
- Os seguintes itens do pedido completo foram enviados por Amazon.com.br para:
- Número do pedido: 702-3877609-2537851
- Quantidade
- Item do pedido
- Enviado por
- 1
- Roaxkois Roda de cerâmica para crianças - Kit completo de pintura de artes e artesanato DIY com argila seca ao ar, tintas, ferramentas, avental e ad
- SKYPOSTAL
- Rastreamento: SKAMZUS0075085120
-Observe que a entrega durante o fim de semana não está disponível para nossas opções de Entrega em dois dias ou Entrega no dia seguinte. Os pacotes enviados de um centro de distribuição no sábado ou domingo só chegarão ao remetente na segunda-feira de manhã.
-Para obter ajuda com seu pedido, você pode encontrar links para enviar um e-mail ou ligar para o Suporte técnico de conta no link Fale conosco no Seller Central.
-Obrigado.
-Equipe do programa FBA - Logística da Amazon
- Este e-m</t>
-        </is>
-      </c>
-    </row>
-    <row r="122">
-      <c r="A122" s="2" t="inlineStr">
-        <is>
-          <t>货件/库存类</t>
-        </is>
-      </c>
-      <c r="B122" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C122" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D122" s="2" t="inlineStr">
-        <is>
-          <t>Mon, 6 Apr 2026 22:48:38 +0000</t>
-        </is>
-      </c>
-      <c r="E122" s="2" t="inlineStr">
-        <is>
-          <t>Fulfilment by Amazon &lt;donotreply@amazon.com&gt;</t>
-        </is>
-      </c>
-      <c r="F122" s="2" t="inlineStr">
-        <is>
-          <t>Remove aged, stranded and unfulfillable inventory by April 30</t>
-        </is>
-      </c>
-      <c r="G122" s="2" t="inlineStr"/>
-      <c r="H122" s="2" t="inlineStr">
         <is>
           <t>96
  Take action now to avoid automatic removal of your Fulfilment by Amazon inventory.
@@ -6473,39 +6414,39 @@
         </is>
       </c>
     </row>
-    <row r="123">
-      <c r="A123" s="2" t="inlineStr">
+    <row r="122">
+      <c r="A122" s="2" t="inlineStr">
         <is>
           <t>货件/库存类</t>
         </is>
       </c>
-      <c r="B123" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C123" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D123" s="2" t="inlineStr">
+      <c r="B122" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C122" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D122" s="2" t="inlineStr">
         <is>
           <t>Fri, 27 Mar 2026 09:57:24 +0000</t>
         </is>
       </c>
-      <c r="E123" s="2" t="inlineStr">
+      <c r="E122" s="2" t="inlineStr">
         <is>
           <t>Fulfilment by Amazon &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F123" s="2" t="inlineStr">
+      <c r="F122" s="2" t="inlineStr">
         <is>
           <t>Create FBA removal order by 2026-04-09</t>
         </is>
       </c>
-      <c r="G123" s="2" t="inlineStr"/>
-      <c r="H123" s="2" t="inlineStr">
+      <c r="G122" s="2" t="inlineStr"/>
+      <c r="H122" s="2" t="inlineStr">
         <is>
           <t>96
 Automated removals of unfulfillable inventory
@@ -6526,39 +6467,39 @@
         </is>
       </c>
     </row>
-    <row r="124">
-      <c r="A124" s="2" t="inlineStr">
+    <row r="123">
+      <c r="A123" s="2" t="inlineStr">
         <is>
           <t>货件/库存类</t>
         </is>
       </c>
-      <c r="B124" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C124" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D124" s="2" t="inlineStr">
+      <c r="B123" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C123" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D123" s="2" t="inlineStr">
         <is>
           <t>Fri, 27 Mar 2026 09:55:39 +0000</t>
         </is>
       </c>
-      <c r="E124" s="2" t="inlineStr">
+      <c r="E123" s="2" t="inlineStr">
         <is>
           <t>Fulfilment by Amazon &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F124" s="2" t="inlineStr">
+      <c r="F123" s="2" t="inlineStr">
         <is>
           <t>Disposal order created for unsellable FBA inventory</t>
         </is>
       </c>
-      <c r="G124" s="2" t="inlineStr"/>
-      <c r="H124" s="2" t="inlineStr">
+      <c r="G123" s="2" t="inlineStr"/>
+      <c r="H123" s="2" t="inlineStr">
         <is>
           <t>96
 Automated Removals of Unfulfillable Inventory
@@ -6581,39 +6522,39 @@
         </is>
       </c>
     </row>
-    <row r="125">
-      <c r="A125" s="2" t="inlineStr">
+    <row r="124">
+      <c r="A124" s="2" t="inlineStr">
         <is>
           <t>货件/库存类</t>
         </is>
       </c>
-      <c r="B125" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C125" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D125" s="2" t="inlineStr">
+      <c r="B124" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C124" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D124" s="2" t="inlineStr">
         <is>
           <t>Fri, 20 Mar 2026 10:45:50 +0000</t>
         </is>
       </c>
-      <c r="E125" s="2" t="inlineStr">
+      <c r="E124" s="2" t="inlineStr">
         <is>
           <t>Fulfilment by Amazon &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F125" s="2" t="inlineStr">
+      <c r="F124" s="2" t="inlineStr">
         <is>
           <t>Create FBA removal order by 2026-04-02</t>
         </is>
       </c>
-      <c r="G125" s="2" t="inlineStr"/>
-      <c r="H125" s="2" t="inlineStr">
+      <c r="G124" s="2" t="inlineStr"/>
+      <c r="H124" s="2" t="inlineStr">
         <is>
           <t>96
 Automated removals of unfulfillable inventory
@@ -6634,39 +6575,39 @@
         </is>
       </c>
     </row>
-    <row r="126">
-      <c r="A126" s="2" t="inlineStr">
+    <row r="125">
+      <c r="A125" s="2" t="inlineStr">
         <is>
           <t>货件/库存类</t>
         </is>
       </c>
-      <c r="B126" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C126" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D126" s="2" t="inlineStr">
+      <c r="B125" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C125" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D125" s="2" t="inlineStr">
         <is>
           <t>Fri, 20 Mar 2026 10:04:22 +0000</t>
         </is>
       </c>
-      <c r="E126" s="2" t="inlineStr">
+      <c r="E125" s="2" t="inlineStr">
         <is>
           <t>Fulfilment by Amazon &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F126" s="2" t="inlineStr">
+      <c r="F125" s="2" t="inlineStr">
         <is>
           <t>Disposal order created for unsellable FBA inventory</t>
         </is>
       </c>
-      <c r="G126" s="2" t="inlineStr"/>
-      <c r="H126" s="2" t="inlineStr">
+      <c r="G125" s="2" t="inlineStr"/>
+      <c r="H125" s="2" t="inlineStr">
         <is>
           <t>96
 Automated Removals of Unfulfillable Inventory
@@ -6690,39 +6631,39 @@
         </is>
       </c>
     </row>
-    <row r="127">
-      <c r="A127" s="2" t="inlineStr">
+    <row r="126">
+      <c r="A126" s="2" t="inlineStr">
         <is>
           <t>货件/库存类</t>
         </is>
       </c>
-      <c r="B127" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C127" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D127" s="2" t="inlineStr">
+      <c r="B126" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C126" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D126" s="2" t="inlineStr">
         <is>
           <t>Fri, 20 Mar 2026 09:25:34 +0000</t>
         </is>
       </c>
-      <c r="E127" s="2" t="inlineStr">
+      <c r="E126" s="2" t="inlineStr">
         <is>
           <t>Fulfilment by Amazon &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F127" s="2" t="inlineStr">
+      <c r="F126" s="2" t="inlineStr">
         <is>
           <t>Disposal order created for unsellable FBA inventory</t>
         </is>
       </c>
-      <c r="G127" s="2" t="inlineStr"/>
-      <c r="H127" s="2" t="inlineStr">
+      <c r="G126" s="2" t="inlineStr"/>
+      <c r="H126" s="2" t="inlineStr">
         <is>
           <t>96
 Automated Removals of Unfulfillable Inventory
@@ -6745,6 +6686,58 @@
         </is>
       </c>
     </row>
+    <row r="127">
+      <c r="A127" s="2" t="inlineStr">
+        <is>
+          <t>其他风险类</t>
+        </is>
+      </c>
+      <c r="B127" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C127" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D127" s="2" t="inlineStr">
+        <is>
+          <t>Thu, 9 Apr 2026 11:27:28 +0000</t>
+        </is>
+      </c>
+      <c r="E127" s="2" t="inlineStr">
+        <is>
+          <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
+        </is>
+      </c>
+      <c r="F127" s="2" t="inlineStr">
+        <is>
+          <t>FBA removal and disposal fees to be charged as units are processed</t>
+        </is>
+      </c>
+      <c r="G127" s="2" t="inlineStr"/>
+      <c r="H127" s="2" t="inlineStr">
+        <is>
+          <t>96
+ FBA removal and disposal fees will now be charged on a per-unit basis at the time each unit is removed or disposed of.
+ Hello,
+ Effective May 1, 2026, Fulfillment by Amazon (FBA) removal and disposal fees will be charged on a per-unit basis at the time each unit is removed or disposed of. This update is in line with industry standards and gives you more visibility into your removal and disposal activities.
+ This change only affects when you are charged. The fee rates for removal and disposal fees remain unchanged. Previously, these fees were charged once the entire removal or disposal order was completed.
+ No action is required from you. This change will apply automatically to new removal and disposal orders created on or after May 1.
+ To review your removal and disposal shipment level charges and when units are removed, go to Transaction view .
+ For more information, go to FBA Removal and Disposal fee updates .
+ The Amazon Europe team
+ Report an issue with this email
+ If you have any questions visit: Seller Central
+ To change your email preferences visit: Notification Preferences
+ Copyright 2026 Amazon, Inc, or its affiliates. All rights reserved.
+ Amazon EU S.à r.l.
+38 avenue</t>
+        </is>
+      </c>
+    </row>
     <row r="128">
       <c r="A128" s="2" t="inlineStr">
         <is>
@@ -6763,21 +6756,72 @@
       </c>
       <c r="D128" s="2" t="inlineStr">
         <is>
-          <t>Tue, 7 Apr 2026 09:23:39 +0000</t>
+          <t>Thu, 9 Apr 2026 10:52:42 +0000</t>
         </is>
       </c>
       <c r="E128" s="2" t="inlineStr">
         <is>
-          <t>Amazon Europe &lt;donotreply@amazon.com&gt;</t>
+          <t>Amazon Services Europe &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
       <c r="F128" s="2" t="inlineStr">
         <is>
-          <t>Update to FBA item package dimensions</t>
+          <t>FBA removal and disposal fees to be charged as units are processed</t>
         </is>
       </c>
       <c r="G128" s="2" t="inlineStr"/>
       <c r="H128" s="2" t="inlineStr">
+        <is>
+          <t>96
+ FBA removal and disposal fees will now be charged on a per-unit basis at the time that each unit is removed or disposed of.
+ Hello,
+ Effective as of May 1, 2026, Fulfilment by Amazon (FBA) removal and disposal fees will be charged on a per-unit basis at the time that each unit is removed or disposed of. This update is in line with industry standards and gives you more visibility into your removal and disposal activities.
+ This change only affects when you are charged. The fee rates for removal and disposal fees remain unchanged. Previously, these fees were charged once the entire removal or disposal order was completed.
+ No action is required from you. This change will apply automatically to new removal and disposal orders created on or after May 1.
+ To review your removal and disposal shipment-level charges and when units are removed, go to Transaction view .
+ For more information, go to FBA removal and disposal fee updates .
+ The Amazon Europe team
+ Report an issue with this email
+ If you have any questions visit: Seller Central
+ To change your email preferences visit: Notification Preferences
+ Copyright 2026 Amazon, Inc, or its affiliates. All rights reserved.
+ Amazon EU S.à</t>
+        </is>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" s="2" t="inlineStr">
+        <is>
+          <t>其他风险类</t>
+        </is>
+      </c>
+      <c r="B129" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C129" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D129" s="2" t="inlineStr">
+        <is>
+          <t>Tue, 7 Apr 2026 09:23:39 +0000</t>
+        </is>
+      </c>
+      <c r="E129" s="2" t="inlineStr">
+        <is>
+          <t>Amazon Europe &lt;donotreply@amazon.com&gt;</t>
+        </is>
+      </c>
+      <c r="F129" s="2" t="inlineStr">
+        <is>
+          <t>Update to FBA item package dimensions</t>
+        </is>
+      </c>
+      <c r="G129" s="2" t="inlineStr"/>
+      <c r="H129" s="2" t="inlineStr">
         <is>
           <t>Update to FBA item package dimensions
  96
@@ -6786,39 +6830,39 @@
         </is>
       </c>
     </row>
-    <row r="129">
-      <c r="A129" s="2" t="inlineStr">
+    <row r="130">
+      <c r="A130" s="2" t="inlineStr">
         <is>
           <t>其他风险类</t>
         </is>
       </c>
-      <c r="B129" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C129" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D129" s="2" t="inlineStr">
+      <c r="B130" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C130" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D130" s="2" t="inlineStr">
         <is>
           <t>Fri, 3 Apr 2026 09:46:59 +0000</t>
         </is>
       </c>
-      <c r="E129" s="2" t="inlineStr">
+      <c r="E130" s="2" t="inlineStr">
         <is>
           <t>Amazon Europe &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F129" s="2" t="inlineStr">
+      <c r="F130" s="2" t="inlineStr">
         <is>
           <t>C2S2 RXO Partner Broker fees increasing in May 2026</t>
         </is>
       </c>
-      <c r="G129" s="2" t="inlineStr"/>
-      <c r="H129" s="2" t="inlineStr">
+      <c r="G130" s="2" t="inlineStr"/>
+      <c r="H130" s="2" t="inlineStr">
         <is>
           <t>Amazon Services
  96
@@ -6836,39 +6880,39 @@
         </is>
       </c>
     </row>
-    <row r="130">
-      <c r="A130" s="2" t="inlineStr">
+    <row r="131">
+      <c r="A131" s="2" t="inlineStr">
         <is>
           <t>其他风险类</t>
         </is>
       </c>
-      <c r="B130" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C130" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D130" s="2" t="inlineStr">
+      <c r="B131" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C131" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D131" s="2" t="inlineStr">
         <is>
           <t>Wed, 1 Apr 2026 00:16:39 +0000</t>
         </is>
       </c>
-      <c r="E130" s="2" t="inlineStr">
+      <c r="E131" s="2" t="inlineStr">
         <is>
           <t>"Amazon.com" &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F130" s="2" t="inlineStr">
+      <c r="F131" s="2" t="inlineStr">
         <is>
           <t>View your US Q2-2026 CSBA fee rate</t>
         </is>
       </c>
-      <c r="G130" s="2" t="inlineStr"/>
-      <c r="H130" s="2" t="inlineStr">
+      <c r="G131" s="2" t="inlineStr"/>
+      <c r="H131" s="2" t="inlineStr">
         <is>
           <t>96
  (Important) CSBA US Fee rate for Q2-2026
@@ -6898,39 +6942,39 @@
         </is>
       </c>
     </row>
-    <row r="131">
-      <c r="A131" s="2" t="inlineStr">
+    <row r="132">
+      <c r="A132" s="2" t="inlineStr">
         <is>
           <t>其他风险类</t>
         </is>
       </c>
-      <c r="B131" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C131" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D131" s="2" t="inlineStr">
+      <c r="B132" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C132" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D132" s="2" t="inlineStr">
         <is>
           <t>Fri, 27 Mar 2026 18:36:24 +0000</t>
         </is>
       </c>
-      <c r="E131" s="2" t="inlineStr">
+      <c r="E132" s="2" t="inlineStr">
         <is>
           <t>"fba-3p-buyability-improvement-ca@amazon.com" &lt;fba-3p-buyability-improvement-ca@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F131" s="2" t="inlineStr">
+      <c r="F132" s="2" t="inlineStr">
         <is>
           <t>[Action Required] – Update Inventory -FBA</t>
         </is>
       </c>
-      <c r="G131" s="2" t="inlineStr"/>
-      <c r="H131" s="2" t="inlineStr">
+      <c r="G132" s="2" t="inlineStr"/>
+      <c r="H132" s="2" t="inlineStr">
         <is>
           <t>Dear Seller,
 This is an email regarding FBA Offers for your Amazon Seller account. We are contacting you to let you know that you could be missing out on sales opportunities because of low/missing inventory for your ASIN offers in the attached sheet.
@@ -6946,39 +6990,39 @@
         </is>
       </c>
     </row>
-    <row r="132">
-      <c r="A132" s="2" t="inlineStr">
+    <row r="133">
+      <c r="A133" s="2" t="inlineStr">
         <is>
           <t>其他风险类</t>
         </is>
       </c>
-      <c r="B132" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C132" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D132" s="2" t="inlineStr">
+      <c r="B133" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C133" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D133" s="2" t="inlineStr">
         <is>
           <t>Sun, 22 Mar 2026 03:22:21 +0000</t>
         </is>
       </c>
-      <c r="E132" s="2" t="inlineStr">
+      <c r="E133" s="2" t="inlineStr">
         <is>
           <t>"fba-3p-buyability-improvement-ca@amazon.com" &lt;fba-3p-buyability-improvement-ca@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F132" s="2" t="inlineStr">
+      <c r="F133" s="2" t="inlineStr">
         <is>
           <t>[Action Required] – Update Inventory -FBA</t>
         </is>
       </c>
-      <c r="G132" s="2" t="inlineStr"/>
-      <c r="H132" s="2" t="inlineStr">
+      <c r="G133" s="2" t="inlineStr"/>
+      <c r="H133" s="2" t="inlineStr">
         <is>
           <t>Dear Seller,
 This is an email regarding FBA Offers for your Amazon Seller account. We are contacting you to let you know that you could be missing out on sales opportunities because of low/missing inventory for your ASIN offers in the attached sheet.
